--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_20_43.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_20_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4157875.838303305</v>
+        <v>4126998.593593336</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7364703.664208709</v>
+        <v>7364703.664208706</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7364703.664208709</v>
+        <v>7364703.664208706</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43001366.31299634</v>
+        <v>43001366.31299635</v>
       </c>
     </row>
   </sheetData>
@@ -663,22 +663,22 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G2" t="n">
-        <v>3.226719020684527</v>
+        <v>403.2267190206845</v>
       </c>
       <c r="H2" t="n">
-        <v>123.1072513769577</v>
+        <v>402.5751059397083</v>
       </c>
       <c r="I2" t="n">
-        <v>129.6231496324334</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>258.699736995617</v>
+        <v>561.4848043710077</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -687,25 +687,25 @@
         <v>615.2589346733669</v>
       </c>
       <c r="M2" t="n">
-        <v>316.5765361412227</v>
+        <v>89.8130117402261</v>
       </c>
       <c r="N2" t="n">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>679.8387640464542</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>622.9784570256061</v>
       </c>
       <c r="Q2" t="n">
         <v>198.6660281433388</v>
       </c>
       <c r="R2" t="n">
-        <v>217.5449505870885</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>482.7559064957902</v>
+        <v>150.4561521525615</v>
       </c>
       <c r="T2" t="n">
         <v>184.3526470551971</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.4556113467254</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>207.3509141932353</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>136.8365481093475</v>
       </c>
       <c r="R3" t="n">
-        <v>507.3765364454635</v>
+        <v>129.645570877285</v>
       </c>
       <c r="S3" t="n">
         <v>61.29022637970564</v>
@@ -793,13 +793,13 @@
         <v>0.1916805149037373</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>235.9784630189306</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>83.31889009107448</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>258.6589137217201</v>
       </c>
       <c r="Q4" t="n">
-        <v>191.6999786948807</v>
+        <v>305.907266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>315.8993083090199</v>
+        <v>285.0109106693754</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -900,19 +900,19 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>403.2267190206845</v>
+        <v>253.3820140903672</v>
       </c>
       <c r="H5" t="n">
         <v>2.575105939708294</v>
       </c>
       <c r="I5" t="n">
-        <v>129.6231496324334</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>685.0898999999999</v>
@@ -921,22 +921,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>615.2589346733669</v>
       </c>
       <c r="M5" t="n">
         <v>89.8130117402261</v>
       </c>
       <c r="N5" t="n">
-        <v>491.6538390443745</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>679.8387640464542</v>
       </c>
       <c r="P5" t="n">
-        <v>622.9784570256061</v>
+        <v>12.94948953995265</v>
       </c>
       <c r="Q5" t="n">
-        <v>198.6660281433388</v>
+        <v>685.0898999999999</v>
       </c>
       <c r="R5" t="n">
         <v>217.5449505870885</v>
@@ -945,7 +945,7 @@
         <v>482.7559064957902</v>
       </c>
       <c r="T5" t="n">
-        <v>304.8847924924466</v>
+        <v>184.3526470551971</v>
       </c>
       <c r="U5" t="n">
         <v>249.1788442873042</v>
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>76.27603335691113</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>4.213350123174166</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1916805149037373</v>
+        <v>400.1916805149037</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1036,10 +1036,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>207.2015992546745</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>83.31889009107448</v>
       </c>
       <c r="N7" t="n">
         <v>134.7595670749636</v>
@@ -1094,7 +1094,7 @@
         <v>258.6589137217201</v>
       </c>
       <c r="Q7" t="n">
-        <v>249.3578984000135</v>
+        <v>166.0390083089362</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.226719020684552</v>
+        <v>123.7588644579339</v>
       </c>
       <c r="H8" t="n">
-        <v>2.575105939708314</v>
+        <v>402.5751059397083</v>
       </c>
       <c r="I8" t="n">
         <v>129.6231496324334</v>
@@ -1155,13 +1155,13 @@
         <v>685.0898999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>631.4989145728644</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>463.9721455435705</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>89.8130117402261</v>
+        <v>562.3056148310548</v>
       </c>
       <c r="N8" t="n">
         <v>699</v>
@@ -1170,19 +1170,19 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>622.9784570256061</v>
       </c>
       <c r="Q8" t="n">
         <v>198.6660281433388</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>217.5449505870885</v>
       </c>
       <c r="S8" t="n">
         <v>482.7559064957902</v>
       </c>
       <c r="T8" t="n">
-        <v>522.4297430795352</v>
+        <v>184.3526470551971</v>
       </c>
       <c r="U8" t="n">
         <v>249.1788442873041</v>
@@ -1207,22 +1207,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>203.5369402411394</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.4556113467254</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>136.8365481093475</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>129.645570877285</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>104.3376673237505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>83.31889009107448</v>
       </c>
       <c r="N10" t="n">
-        <v>20.96980446208494</v>
+        <v>134.7595670749636</v>
       </c>
       <c r="O10" t="n">
         <v>206.8007116199985</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>258.6589137217201</v>
       </c>
       <c r="Q10" t="n">
-        <v>305.907266425598</v>
+        <v>166.0390083089479</v>
       </c>
       <c r="R10" t="n">
-        <v>315.8993083090199</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>269.9993129555745</v>
+        <v>103.0230852833748</v>
       </c>
       <c r="C11" t="n">
-        <v>237.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>198.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>191.2267190206846</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>437.1788442873041</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>417.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>426.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>4.116176951763522</v>
+        <v>380.2818334606677</v>
       </c>
       <c r="Y11" t="n">
         <v>299.3174326828064</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6.38713997450235</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>271.3188900910745</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>277.7060300655768</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1608,19 +1608,19 @@
         <v>231.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>192.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>186.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>186.8896287080119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>184.5751059397083</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>151.7894684554557</v>
       </c>
       <c r="T14" t="n">
-        <v>101.6275922831731</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>431.1788442873042</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>411.8510241668239</v>
@@ -1696,7 +1696,7 @@
         <v>121.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>107.4556113467254</v>
+        <v>107.4556113467255</v>
       </c>
       <c r="H15" t="n">
         <v>111.425973978874</v>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>69.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>54.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>67.53621805555548</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>8.654798232766154</v>
+        <v>8.65479823276616</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1808,10 +1808,10 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>319.1090300655768</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>28.82476674532812</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1826,10 +1826,10 @@
         <v>8.372809838709685</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>29.44364543010755</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>69.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -1857,7 +1857,7 @@
         <v>94.22671902068456</v>
       </c>
       <c r="H17" t="n">
-        <v>93.57510593970831</v>
+        <v>87.2753515964793</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>199.1480805282748</v>
       </c>
       <c r="L17" t="n">
-        <v>199.1480805282354</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>283.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>196.0176783395773</v>
+        <v>202.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>356.0485091283007</v>
+        <v>75.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>52.09991244551929</v>
@@ -1930,7 +1930,7 @@
         <v>33.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>30.63624233787687</v>
+        <v>174.2916467105027</v>
       </c>
       <c r="G18" t="n">
         <v>16.45561134672545</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>136.8365481093475</v>
       </c>
       <c r="R18" t="n">
         <v>220.645570877285</v>
@@ -2027,28 +2027,28 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>79.15864455122178</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>174.3188900910745</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>225.7595670749636</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>297.8007116199985</v>
+        <v>123.2268941610084</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>349.6589137217201</v>
       </c>
       <c r="Q19" t="n">
         <v>396.907266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>53.52208544671635</v>
+        <v>406.8993083090199</v>
       </c>
       <c r="S19" t="n">
-        <v>49.22521740777347</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2091,10 +2091,10 @@
         <v>95.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>94.22671902068456</v>
+        <v>94.22671902068453</v>
       </c>
       <c r="H20" t="n">
-        <v>93.57510593970831</v>
+        <v>91.15615159647932</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2103,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4.133005151485581</v>
       </c>
       <c r="L20" t="n">
-        <v>4.133005151411392</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
         <v>275.3526470551971</v>
       </c>
       <c r="U20" t="n">
-        <v>337.7598899440751</v>
+        <v>340.1788442873042</v>
       </c>
       <c r="V20" t="n">
         <v>320.8510241668239</v>
@@ -2158,7 +2158,7 @@
         <v>75.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>52.09991244551929</v>
+        <v>332.5918649274933</v>
       </c>
       <c r="D21" t="n">
         <v>38.93768689770263</v>
@@ -2173,7 +2173,7 @@
         <v>16.45561134672545</v>
       </c>
       <c r="H21" t="n">
-        <v>20.42597397887396</v>
+        <v>20.42597397887397</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         <v>220.645570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>432.7821788616793</v>
+        <v>152.2902263797056</v>
       </c>
       <c r="T21" t="n">
-        <v>95.21335012317419</v>
+        <v>95.21335012317417</v>
       </c>
       <c r="U21" t="n">
-        <v>91.19168051490372</v>
+        <v>91.19168051490374</v>
       </c>
       <c r="V21" t="n">
         <v>105.5106671915202</v>
@@ -2273,13 +2273,13 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>123.2268941610084</v>
+        <v>297.8007116199985</v>
       </c>
       <c r="P22" t="n">
         <v>349.6589137217201</v>
       </c>
       <c r="Q22" t="n">
-        <v>396.907266425598</v>
+        <v>222.3334489666078</v>
       </c>
       <c r="R22" t="n">
         <v>406.8993083090199</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>170.5803586123455</v>
+        <v>170.5803586123454</v>
       </c>
       <c r="C23" t="n">
         <v>140.4745782429939</v>
@@ -2328,10 +2328,10 @@
         <v>95.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>94.22671902068453</v>
+        <v>94.22671902068456</v>
       </c>
       <c r="H23" t="n">
-        <v>93.57510593970829</v>
+        <v>93.57510593970831</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>4.133005151521149</v>
+        <v>4.133005151438688</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>275.3526470551971</v>
       </c>
       <c r="U23" t="n">
-        <v>340.1788442873042</v>
+        <v>340.1788442873041</v>
       </c>
       <c r="V23" t="n">
         <v>320.8510241668239</v>
@@ -2410,7 +2410,7 @@
         <v>16.45561134672545</v>
       </c>
       <c r="H24" t="n">
-        <v>300.9179264608479</v>
+        <v>20.42597397887396</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2446,10 +2446,10 @@
         <v>152.2902263797056</v>
       </c>
       <c r="T24" t="n">
-        <v>95.21335012317417</v>
+        <v>95.21335012317419</v>
       </c>
       <c r="U24" t="n">
-        <v>91.19168051490374</v>
+        <v>371.6836329968776</v>
       </c>
       <c r="V24" t="n">
         <v>105.5106671915202</v>
@@ -2553,13 +2553,13 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>207.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>153.9578399766353</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>162.3632896068686</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>160.5751059397083</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>240.7559064957902</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>342.3526470551971</v>
       </c>
       <c r="U26" t="n">
-        <v>396.0000000000027</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>387.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>396.0000000000024</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>87.62834315036456</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>269.3174326828064</v>
@@ -2641,7 +2641,7 @@
         <v>100.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>97.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>83.45561134672546</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>99.32070521588223</v>
       </c>
       <c r="S27" t="n">
         <v>219.2902263797056</v>
@@ -2686,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>158.1916805149037</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>16.00344955462188</v>
+        <v>172.5106671915202</v>
       </c>
       <c r="W27" t="n">
         <v>190.3731429098285</v>
@@ -2708,19 +2708,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>45.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>30.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>43.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>38.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>32.38285596774193</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2750,16 +2750,16 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>88.10467946619922</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>131.675083363586</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>116.2252174077735</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>45.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -2787,22 +2787,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>239.9993129555745</v>
       </c>
       <c r="C29" t="n">
         <v>207.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>99.15892493074521</v>
+        <v>168.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>162.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>162.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>161.2267190206846</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>160.5751059397083</v>
@@ -2841,7 +2841,7 @@
         <v>240.7559064957902</v>
       </c>
       <c r="T29" t="n">
-        <v>342.3526470551971</v>
+        <v>87.44567923526471</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>269.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>142.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>119.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>105.9376868977026</v>
@@ -2881,7 +2881,7 @@
         <v>97.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>83.45561134672546</v>
+        <v>83.45561134672545</v>
       </c>
       <c r="H30" t="n">
         <v>87.42597397887397</v>
@@ -2914,25 +2914,25 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>287.645570877285</v>
+        <v>174.1951300695255</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>219.2902263797056</v>
       </c>
       <c r="T30" t="n">
-        <v>162.2133501231742</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>158.1916805149037</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>172.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>4.616614298371556</v>
+        <v>190.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>177.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>157.3913927661343</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>292.7595670749636</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>191.3451123912356</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>88.10467946619922</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>239.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>207.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>168.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>162.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -3081,16 +3081,16 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>396.000000000002</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>387.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>139.0211973112389</v>
+        <v>395.9999999999999</v>
       </c>
       <c r="X32" t="n">
-        <v>350.2818334606677</v>
+        <v>87.62834315036777</v>
       </c>
       <c r="Y32" t="n">
         <v>269.3174326828064</v>
@@ -3109,16 +3109,16 @@
         <v>119.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>105.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>100.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>97.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>83.45561134672546</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3151,10 +3151,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>173.1417466104801</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>142.7244744095418</v>
       </c>
       <c r="T33" t="n">
         <v>162.2133501231742</v>
@@ -3166,7 +3166,7 @@
         <v>172.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>190.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>177.8627394453875</v>
@@ -3182,16 +3182,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>45.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>30.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>43.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>38.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3227,13 +3227,13 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>88.10467946619922</v>
       </c>
       <c r="R34" t="n">
-        <v>164.057939331328</v>
+        <v>396</v>
       </c>
       <c r="S34" t="n">
-        <v>116.2252174077735</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>45.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>160.5751059397083</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,25 +3312,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>240.7559064957902</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>133.3465096897021</v>
       </c>
       <c r="U35" t="n">
-        <v>389.1839541038311</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>387.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>396.0000000000024</v>
+        <v>395.9999999999999</v>
       </c>
       <c r="X35" t="n">
         <v>350.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>269.3174326828064</v>
       </c>
     </row>
     <row r="36">
@@ -3340,19 +3340,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>142.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>119.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>105.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>100.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>97.63624233787687</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>287.645570877285</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>219.2902263797056</v>
+        <v>55.29850043066823</v>
       </c>
       <c r="T36" t="n">
         <v>162.2133501231742</v>
@@ -3403,7 +3403,7 @@
         <v>172.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>114.2651987230151</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>177.8627394453875</v>
@@ -3452,13 +3452,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>191.3451123912356</v>
       </c>
       <c r="N37" t="n">
-        <v>119.3039678462006</v>
+        <v>292.7595670749636</v>
       </c>
       <c r="O37" t="n">
-        <v>364.8007116199985</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3498,25 +3498,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>239.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>207.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>168.3391557398498</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>162.3632896068686</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>162.8896287080119</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>39.15572880699074</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>160.5751059397083</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3552,22 +3552,22 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>342.3526470551971</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>141.2756960951711</v>
+        <v>396.000000000002</v>
       </c>
       <c r="V38" t="n">
-        <v>387.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>396.0000000000015</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>269.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3592,10 +3592,10 @@
         <v>97.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>83.45561134672546</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>59.26886306281657</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>142.7244744095418</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3689,13 +3689,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>191.3451123912356</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>292.7595670749636</v>
+        <v>119.3039678462006</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>364.8007116199985</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>285.4019807597907</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>306.2267190206845</v>
       </c>
       <c r="H41" t="n">
-        <v>305.5751059397083</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>32.62314963243335</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3789,19 +3789,19 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>396.0000000000063</v>
+        <v>396.0000000000013</v>
       </c>
       <c r="U41" t="n">
-        <v>396.0000000000054</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>396.0000000000016</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>318.6767434731916</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>174.0642804064719</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>250.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>245.6720972219126</v>
@@ -3832,7 +3832,7 @@
         <v>228.4556113467254</v>
       </c>
       <c r="H42" t="n">
-        <v>232.425973978874</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>110.3509141932353</v>
@@ -3862,16 +3862,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>396.0000000000015</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>62.7442480025453</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>303.1916805149037</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>23.05121814196066</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>76.9966258098612</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>53.94540766790055</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>390.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>358.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>319.3391557398498</v>
@@ -3987,13 +3987,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>312.2267190206845</v>
       </c>
       <c r="H44" t="n">
-        <v>311.5751059397083</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>25.98289653478497</v>
+        <v>38.62314963243335</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>126.5449505870884</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>391.7559064957902</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>75.97106911124033</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>395.0000000000016</v>
       </c>
     </row>
     <row r="45">
@@ -4054,7 +4054,7 @@
         <v>293.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>192.2121057562256</v>
+        <v>270.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4063,16 +4063,16 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>248.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>234.4556113467254</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>116.3509141932353</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4105,10 +4105,10 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>313.2133501231742</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>309.1916805149037</v>
+        <v>177.7762844574174</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4151,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>71.11602580986123</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4184,10 +4184,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>11.17061814196066</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>59.94540766790056</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4297,46 +4297,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>788.2672447755554</v>
+        <v>1343.665936624361</v>
       </c>
       <c r="C2" t="n">
-        <v>738.2929233179857</v>
+        <v>1293.691615166791</v>
       </c>
       <c r="D2" t="n">
-        <v>727.8493316615718</v>
+        <v>1283.248023510377</v>
       </c>
       <c r="E2" t="n">
-        <v>319.4015643819065</v>
+        <v>1278.840660271116</v>
       </c>
       <c r="F2" t="n">
-        <v>314.4625454849248</v>
+        <v>869.8612373337302</v>
       </c>
       <c r="G2" t="n">
-        <v>311.2032333428193</v>
+        <v>462.5615211512205</v>
       </c>
       <c r="H2" t="n">
-        <v>186.8524743761953</v>
+        <v>55.92</v>
       </c>
       <c r="I2" t="n">
         <v>55.92</v>
       </c>
       <c r="J2" t="n">
-        <v>486.6171343478616</v>
+        <v>180.7736319484769</v>
       </c>
       <c r="K2" t="n">
-        <v>1178.627134347862</v>
+        <v>872.7836319484769</v>
       </c>
       <c r="L2" t="n">
-        <v>1249.163462960622</v>
+        <v>943.3199605612376</v>
       </c>
       <c r="M2" t="n">
-        <v>1621.399184030094</v>
+        <v>1544.609746682221</v>
       </c>
       <c r="N2" t="n">
-        <v>1607.348577969488</v>
+        <v>2236.619746682221</v>
       </c>
       <c r="O2" t="n">
-        <v>1612.652755700342</v>
+        <v>2241.923924413076</v>
       </c>
       <c r="P2" t="n">
         <v>2304.662755700342</v>
@@ -4345,28 +4345,28 @@
         <v>2796</v>
       </c>
       <c r="R2" t="n">
-        <v>2576.257625669607</v>
+        <v>2796</v>
       </c>
       <c r="S2" t="n">
-        <v>2088.625396885981</v>
+        <v>2644.024088734786</v>
       </c>
       <c r="T2" t="n">
-        <v>1902.410601880732</v>
+        <v>2457.809293729537</v>
       </c>
       <c r="U2" t="n">
-        <v>1650.714799570323</v>
+        <v>2206.113491419128</v>
       </c>
       <c r="V2" t="n">
-        <v>1418.542047886663</v>
+        <v>1973.940739735468</v>
       </c>
       <c r="W2" t="n">
-        <v>1177.760759017019</v>
+        <v>1733.159450865824</v>
       </c>
       <c r="X2" t="n">
-        <v>983.536684814324</v>
+        <v>1538.935376663129</v>
       </c>
       <c r="Y2" t="n">
-        <v>871.0948336195701</v>
+        <v>1426.493525468375</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>420.6673863086054</v>
+        <v>594.108409636324</v>
       </c>
       <c r="C3" t="n">
-        <v>55.92</v>
+        <v>594.108409636324</v>
       </c>
       <c r="D3" t="n">
-        <v>55.92</v>
+        <v>594.108409636324</v>
       </c>
       <c r="E3" t="n">
-        <v>55.92</v>
+        <v>594.108409636324</v>
       </c>
       <c r="F3" t="n">
-        <v>55.92</v>
+        <v>594.108409636324</v>
       </c>
       <c r="G3" t="n">
-        <v>55.92</v>
+        <v>265.3653678719549</v>
       </c>
       <c r="H3" t="n">
-        <v>55.92</v>
+        <v>265.3653678719549</v>
       </c>
       <c r="I3" t="n">
         <v>55.92</v>
@@ -4424,28 +4424,28 @@
         <v>1470.988944904548</v>
       </c>
       <c r="R3" t="n">
-        <v>958.4873929394334</v>
+        <v>1340.033822806281</v>
       </c>
       <c r="S3" t="n">
-        <v>896.5780733639732</v>
+        <v>1278.12450323082</v>
       </c>
       <c r="T3" t="n">
-        <v>892.3221641486458</v>
+        <v>1273.868594015493</v>
       </c>
       <c r="U3" t="n">
-        <v>892.1285474669248</v>
+        <v>1273.674977333772</v>
       </c>
       <c r="V3" t="n">
-        <v>877.4713078795307</v>
+        <v>1035.312893476266</v>
       </c>
       <c r="W3" t="n">
-        <v>844.7711635261686</v>
+        <v>1002.612749122904</v>
       </c>
       <c r="X3" t="n">
-        <v>420.6673863086054</v>
+        <v>982.5493759457449</v>
       </c>
       <c r="Y3" t="n">
-        <v>420.6673863086054</v>
+        <v>982.5493759457449</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>320.4436731116286</v>
+        <v>2335.436159840353</v>
       </c>
       <c r="C4" t="n">
-        <v>446.4456789300644</v>
+        <v>2335.436159840353</v>
       </c>
       <c r="D4" t="n">
-        <v>559.7648230550645</v>
+        <v>2448.755303965353</v>
       </c>
       <c r="E4" t="n">
-        <v>559.7648230550645</v>
+        <v>2448.755303965353</v>
       </c>
       <c r="F4" t="n">
-        <v>559.7648230550645</v>
+        <v>2448.755303965353</v>
       </c>
       <c r="G4" t="n">
-        <v>559.7648230550645</v>
+        <v>2448.755303965353</v>
       </c>
       <c r="H4" t="n">
-        <v>559.7648230550645</v>
+        <v>2448.755303965353</v>
       </c>
       <c r="I4" t="n">
-        <v>559.7648230550645</v>
+        <v>2448.755303965353</v>
       </c>
       <c r="J4" t="n">
-        <v>776.3357125082122</v>
+        <v>2796</v>
       </c>
       <c r="K4" t="n">
-        <v>914.0786775926215</v>
+        <v>2796</v>
       </c>
       <c r="L4" t="n">
-        <v>914.0786775926215</v>
+        <v>2796</v>
       </c>
       <c r="M4" t="n">
-        <v>829.9181825511321</v>
+        <v>2796</v>
       </c>
       <c r="N4" t="n">
-        <v>829.9181825511321</v>
+        <v>2796</v>
       </c>
       <c r="O4" t="n">
-        <v>829.9181825511321</v>
+        <v>2796</v>
       </c>
       <c r="P4" t="n">
-        <v>568.6465525291926</v>
+        <v>2534.728369978061</v>
       </c>
       <c r="Q4" t="n">
-        <v>375.0102104131515</v>
+        <v>2225.731131164325</v>
       </c>
       <c r="R4" t="n">
-        <v>55.92</v>
+        <v>1937.84132240738</v>
       </c>
       <c r="S4" t="n">
-        <v>97.27703476630427</v>
+        <v>1937.84132240738</v>
       </c>
       <c r="T4" t="n">
-        <v>97.27703476630427</v>
+        <v>1937.84132240738</v>
       </c>
       <c r="U4" t="n">
-        <v>97.27703476630427</v>
+        <v>2184.405368816159</v>
       </c>
       <c r="V4" t="n">
-        <v>97.27703476630427</v>
+        <v>2184.405368816159</v>
       </c>
       <c r="W4" t="n">
-        <v>97.27703476630427</v>
+        <v>2184.405368816159</v>
       </c>
       <c r="X4" t="n">
-        <v>97.27703476630427</v>
+        <v>2335.436159840353</v>
       </c>
       <c r="Y4" t="n">
-        <v>208.6863354453365</v>
+        <v>2335.436159840353</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>666.5176029197479</v>
+        <v>788.2672447755554</v>
       </c>
       <c r="C5" t="n">
-        <v>616.5432814621782</v>
+        <v>738.2929233179857</v>
       </c>
       <c r="D5" t="n">
-        <v>606.0996898057643</v>
+        <v>727.8493316615718</v>
       </c>
       <c r="E5" t="n">
-        <v>601.6923265665031</v>
+        <v>319.4015643819065</v>
       </c>
       <c r="F5" t="n">
-        <v>596.7533076695214</v>
+        <v>314.4625454849248</v>
       </c>
       <c r="G5" t="n">
-        <v>189.4535914870117</v>
+        <v>58.52111711081646</v>
       </c>
       <c r="H5" t="n">
-        <v>186.8524743761953</v>
+        <v>55.92</v>
       </c>
       <c r="I5" t="n">
         <v>55.92</v>
@@ -4564,19 +4564,19 @@
         <v>747.9299999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1439.94</v>
+        <v>818.4663286127607</v>
       </c>
       <c r="M5" t="n">
-        <v>2041.229786120984</v>
+        <v>1419.756114733744</v>
       </c>
       <c r="N5" t="n">
-        <v>2236.619746682221</v>
+        <v>2111.766114733744</v>
       </c>
       <c r="O5" t="n">
-        <v>2241.923924413076</v>
+        <v>2117.070292464598</v>
       </c>
       <c r="P5" t="n">
-        <v>2304.662755700342</v>
+        <v>2796</v>
       </c>
       <c r="Q5" t="n">
         <v>2796</v>
@@ -4588,22 +4588,22 @@
         <v>2088.625396885981</v>
       </c>
       <c r="T5" t="n">
-        <v>1780.660960024924</v>
+        <v>1902.410601880732</v>
       </c>
       <c r="U5" t="n">
-        <v>1528.965157714515</v>
+        <v>1650.714799570323</v>
       </c>
       <c r="V5" t="n">
-        <v>1296.792406030855</v>
+        <v>1418.542047886663</v>
       </c>
       <c r="W5" t="n">
-        <v>1056.011117161211</v>
+        <v>1177.760759017019</v>
       </c>
       <c r="X5" t="n">
-        <v>861.7870429585165</v>
+        <v>983.536684814324</v>
       </c>
       <c r="Y5" t="n">
-        <v>749.3451917637626</v>
+        <v>871.0948336195701</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>766.8008178458908</v>
+        <v>132.9664983403143</v>
       </c>
       <c r="C6" t="n">
-        <v>402.0534315372855</v>
+        <v>132.9664983403143</v>
       </c>
       <c r="D6" t="n">
-        <v>402.0534315372855</v>
+        <v>132.9664983403143</v>
       </c>
       <c r="E6" t="n">
-        <v>55.92</v>
+        <v>132.9664983403143</v>
       </c>
       <c r="F6" t="n">
-        <v>55.92</v>
+        <v>132.9664983403143</v>
       </c>
       <c r="G6" t="n">
-        <v>55.92</v>
+        <v>132.9664983403143</v>
       </c>
       <c r="H6" t="n">
-        <v>55.92</v>
+        <v>132.9664983403143</v>
       </c>
       <c r="I6" t="n">
         <v>55.92</v>
@@ -4670,19 +4670,19 @@
         <v>1412.08732947948</v>
       </c>
       <c r="U6" t="n">
-        <v>1411.893712797759</v>
+        <v>1007.853308757355</v>
       </c>
       <c r="V6" t="n">
-        <v>1397.236473210365</v>
+        <v>993.1960691699612</v>
       </c>
       <c r="W6" t="n">
-        <v>1364.536328857003</v>
+        <v>960.4959248165991</v>
       </c>
       <c r="X6" t="n">
-        <v>1155.241784155312</v>
+        <v>536.3921475990359</v>
       </c>
       <c r="Y6" t="n">
-        <v>1155.241784155312</v>
+        <v>132.9664983403143</v>
       </c>
     </row>
     <row r="7">
@@ -4692,49 +4692,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>398.1169302799258</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="C7" t="n">
-        <v>524.1189360983616</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="D7" t="n">
-        <v>637.4380802233617</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="E7" t="n">
-        <v>755.2669844347747</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="F7" t="n">
-        <v>879.6279570267102</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="G7" t="n">
-        <v>879.6279570267102</v>
+        <v>250.9192531122059</v>
       </c>
       <c r="H7" t="n">
-        <v>902.3557356983316</v>
+        <v>250.9192531122059</v>
       </c>
       <c r="I7" t="n">
-        <v>902.3557356983316</v>
+        <v>479.1388441794364</v>
       </c>
       <c r="J7" t="n">
-        <v>902.3557356983316</v>
+        <v>856.8832136843467</v>
       </c>
       <c r="K7" t="n">
-        <v>902.3557356983316</v>
+        <v>902.3557356983288</v>
       </c>
       <c r="L7" t="n">
-        <v>914.0786775926221</v>
+        <v>914.0786775926192</v>
       </c>
       <c r="M7" t="n">
-        <v>914.0786775926221</v>
+        <v>829.9181825511298</v>
       </c>
       <c r="N7" t="n">
-        <v>777.9579027694265</v>
+        <v>693.7974077279342</v>
       </c>
       <c r="O7" t="n">
-        <v>569.0682950724582</v>
+        <v>484.907800030966</v>
       </c>
       <c r="P7" t="n">
-        <v>307.7966650505188</v>
+        <v>223.6361700090265</v>
       </c>
       <c r="Q7" t="n">
         <v>55.92</v>
@@ -4746,22 +4746,22 @@
         <v>97.27703476630427</v>
       </c>
       <c r="T7" t="n">
-        <v>286.3595926136337</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="U7" t="n">
-        <v>286.3595926136337</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="V7" t="n">
-        <v>286.3595926136337</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="W7" t="n">
-        <v>286.3595926136337</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="X7" t="n">
-        <v>286.3595926136337</v>
+        <v>97.27703476630427</v>
       </c>
       <c r="Y7" t="n">
-        <v>286.3595926136337</v>
+        <v>97.27703476630427</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>666.517602919748</v>
+        <v>788.2672447755554</v>
       </c>
       <c r="C8" t="n">
-        <v>212.5028774217743</v>
+        <v>738.2929233179857</v>
       </c>
       <c r="D8" t="n">
-        <v>202.0592857653603</v>
+        <v>727.8493316615718</v>
       </c>
       <c r="E8" t="n">
-        <v>197.6519225260991</v>
+        <v>723.4419684223105</v>
       </c>
       <c r="F8" t="n">
-        <v>192.7129036291174</v>
+        <v>718.5029495253289</v>
       </c>
       <c r="G8" t="n">
-        <v>189.4535914870118</v>
+        <v>593.4939955274158</v>
       </c>
       <c r="H8" t="n">
         <v>186.8524743761953</v>
@@ -4798,19 +4798,19 @@
         <v>55.92</v>
       </c>
       <c r="K8" t="n">
-        <v>110.0523085122582</v>
+        <v>747.9299999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>333.4035756399646</v>
+        <v>1439.94</v>
       </c>
       <c r="M8" t="n">
-        <v>934.6933617609483</v>
+        <v>1563.964530473682</v>
       </c>
       <c r="N8" t="n">
-        <v>920.6427557003421</v>
+        <v>1549.913924413076</v>
       </c>
       <c r="O8" t="n">
-        <v>1612.652755700342</v>
+        <v>2241.923924413076</v>
       </c>
       <c r="P8" t="n">
         <v>2304.662755700342</v>
@@ -4819,28 +4819,28 @@
         <v>2796</v>
       </c>
       <c r="R8" t="n">
-        <v>2796</v>
+        <v>2576.257625669607</v>
       </c>
       <c r="S8" t="n">
-        <v>2308.367771216374</v>
+        <v>2088.625396885981</v>
       </c>
       <c r="T8" t="n">
-        <v>1780.660960024924</v>
+        <v>1902.410601880732</v>
       </c>
       <c r="U8" t="n">
-        <v>1528.965157714515</v>
+        <v>1650.714799570323</v>
       </c>
       <c r="V8" t="n">
-        <v>1296.792406030855</v>
+        <v>1418.542047886663</v>
       </c>
       <c r="W8" t="n">
-        <v>1056.011117161211</v>
+        <v>1177.760759017019</v>
       </c>
       <c r="X8" t="n">
-        <v>861.7870429585165</v>
+        <v>983.536684814324</v>
       </c>
       <c r="Y8" t="n">
-        <v>749.3451917637626</v>
+        <v>871.0948336195701</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1100.862637060553</v>
+        <v>956.0319893704232</v>
       </c>
       <c r="C9" t="n">
-        <v>736.1152507519475</v>
+        <v>956.0319893704232</v>
       </c>
       <c r="D9" t="n">
-        <v>384.6630417643692</v>
+        <v>604.5797803828448</v>
       </c>
       <c r="E9" t="n">
-        <v>384.6630417643692</v>
+        <v>398.9869114524009</v>
       </c>
       <c r="F9" t="n">
-        <v>384.6630417643692</v>
+        <v>55.92</v>
       </c>
       <c r="G9" t="n">
         <v>55.92</v>
@@ -4895,31 +4895,31 @@
         <v>1609.207680368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1470.988944904548</v>
+        <v>1609.207680368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1340.033822806281</v>
+        <v>1478.252558270268</v>
       </c>
       <c r="S9" t="n">
-        <v>1278.12450323082</v>
+        <v>1416.343238694808</v>
       </c>
       <c r="T9" t="n">
-        <v>1273.868594015493</v>
+        <v>1412.08732947948</v>
       </c>
       <c r="U9" t="n">
-        <v>1273.674977333772</v>
+        <v>1411.893712797759</v>
       </c>
       <c r="V9" t="n">
-        <v>1259.017737746378</v>
+        <v>1397.236473210365</v>
       </c>
       <c r="W9" t="n">
-        <v>1226.317593393016</v>
+        <v>1364.536328857003</v>
       </c>
       <c r="X9" t="n">
-        <v>1206.254220215857</v>
+        <v>1344.472955679844</v>
       </c>
       <c r="Y9" t="n">
-        <v>1100.862637060553</v>
+        <v>1344.472955679844</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>914.0786775926277</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="C10" t="n">
-        <v>914.0786775926277</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="D10" t="n">
-        <v>914.0786775926277</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="E10" t="n">
-        <v>914.0786775926277</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="F10" t="n">
-        <v>914.0786775926277</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="G10" t="n">
-        <v>914.0786775926277</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="H10" t="n">
-        <v>914.0786775926277</v>
+        <v>296.3917751261998</v>
       </c>
       <c r="I10" t="n">
-        <v>914.0786775926277</v>
+        <v>524.6113661934303</v>
       </c>
       <c r="J10" t="n">
-        <v>914.0786775926277</v>
+        <v>902.3557356983406</v>
       </c>
       <c r="K10" t="n">
-        <v>914.0786775926277</v>
+        <v>902.3557356983406</v>
       </c>
       <c r="L10" t="n">
-        <v>914.0786775926277</v>
+        <v>914.078677592631</v>
       </c>
       <c r="M10" t="n">
-        <v>914.0786775926277</v>
+        <v>829.9181825511416</v>
       </c>
       <c r="N10" t="n">
-        <v>892.8970569238551</v>
+        <v>693.7974077279461</v>
       </c>
       <c r="O10" t="n">
-        <v>684.0074492268868</v>
+        <v>484.9078000309778</v>
       </c>
       <c r="P10" t="n">
-        <v>684.0074492268868</v>
+        <v>223.6361700090383</v>
       </c>
       <c r="Q10" t="n">
-        <v>375.0102104131514</v>
+        <v>55.92</v>
       </c>
       <c r="R10" t="n">
         <v>55.92</v>
@@ -4983,22 +4983,22 @@
         <v>55.92</v>
       </c>
       <c r="T10" t="n">
-        <v>55.92</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="U10" t="n">
-        <v>302.4840464087785</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="V10" t="n">
-        <v>479.7476676297246</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="W10" t="n">
-        <v>651.638585889402</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="X10" t="n">
-        <v>802.6693769135954</v>
+        <v>245.0025578473295</v>
       </c>
       <c r="Y10" t="n">
-        <v>914.0786775926277</v>
+        <v>245.0025578473295</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>689.2941949530589</v>
+        <v>55.92</v>
       </c>
       <c r="C11" t="n">
-        <v>449.4208835964994</v>
+        <v>55.92</v>
       </c>
       <c r="D11" t="n">
-        <v>249.0783020410955</v>
+        <v>55.92</v>
       </c>
       <c r="E11" t="n">
-        <v>249.0783020410955</v>
+        <v>55.92</v>
       </c>
       <c r="F11" t="n">
-        <v>249.0783020410955</v>
+        <v>55.92</v>
       </c>
       <c r="G11" t="n">
         <v>55.92</v>
@@ -5032,25 +5032,25 @@
         <v>55.92</v>
       </c>
       <c r="J11" t="n">
-        <v>491.8172603743391</v>
+        <v>65.81557115404399</v>
       </c>
       <c r="K11" t="n">
-        <v>558.6433349472035</v>
+        <v>757.825571154044</v>
       </c>
       <c r="L11" t="n">
-        <v>1250.653334947204</v>
+        <v>911.3332983460685</v>
       </c>
       <c r="M11" t="n">
-        <v>1853.74845332438</v>
+        <v>1514.428416723245</v>
       </c>
       <c r="N11" t="n">
-        <v>2545.75845332438</v>
+        <v>2206.438416723245</v>
       </c>
       <c r="O11" t="n">
-        <v>2564.72807691839</v>
+        <v>2225.408040317255</v>
       </c>
       <c r="P11" t="n">
-        <v>2639.989404463041</v>
+        <v>2300.669367861905</v>
       </c>
       <c r="Q11" t="n">
         <v>2796</v>
@@ -5068,16 +5068,16 @@
         <v>1699.199648055172</v>
       </c>
       <c r="V11" t="n">
-        <v>1699.199648055172</v>
+        <v>1277.127906472522</v>
       </c>
       <c r="W11" t="n">
-        <v>1268.519369286538</v>
+        <v>846.4476277038879</v>
       </c>
       <c r="X11" t="n">
-        <v>1264.361614789807</v>
+        <v>462.3245636022033</v>
       </c>
       <c r="Y11" t="n">
-        <v>962.0207736960634</v>
+        <v>159.9837225084594</v>
       </c>
     </row>
     <row r="12">
@@ -5108,22 +5108,22 @@
         <v>55.92</v>
       </c>
       <c r="I12" t="n">
-        <v>55.92</v>
+        <v>60.52259494869703</v>
       </c>
       <c r="J12" t="n">
-        <v>206.4329152696386</v>
+        <v>420.9155102183356</v>
       </c>
       <c r="K12" t="n">
-        <v>503.5747882186037</v>
+        <v>865.3774353693227</v>
       </c>
       <c r="L12" t="n">
-        <v>1045.83650830437</v>
+        <v>1255.71650830437</v>
       </c>
       <c r="M12" t="n">
-        <v>1413.017650047229</v>
+        <v>1622.897650047229</v>
       </c>
       <c r="N12" t="n">
-        <v>1829.283532013288</v>
+        <v>2039.163532013288</v>
       </c>
       <c r="O12" t="n">
         <v>2345.08332294229</v>
@@ -5196,22 +5196,22 @@
         <v>336.4311414803807</v>
       </c>
       <c r="L13" t="n">
-        <v>329.9794849404793</v>
+        <v>336.4311414803807</v>
       </c>
       <c r="M13" t="n">
-        <v>55.92</v>
+        <v>336.4311414803807</v>
       </c>
       <c r="N13" t="n">
-        <v>55.92</v>
+        <v>336.4311414803807</v>
       </c>
       <c r="O13" t="n">
-        <v>55.92</v>
+        <v>336.4311414803807</v>
       </c>
       <c r="P13" t="n">
-        <v>55.92</v>
+        <v>336.4311414803807</v>
       </c>
       <c r="Q13" t="n">
-        <v>55.92</v>
+        <v>336.4311414803807</v>
       </c>
       <c r="R13" t="n">
         <v>55.92</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>476.1722062451538</v>
+        <v>861.0378306037619</v>
       </c>
       <c r="C14" t="n">
-        <v>242.3595009492003</v>
+        <v>627.2251253078084</v>
       </c>
       <c r="D14" t="n">
-        <v>242.3595009492003</v>
+        <v>432.9431498130107</v>
       </c>
       <c r="E14" t="n">
-        <v>242.3595009492003</v>
+        <v>244.6974027353655</v>
       </c>
       <c r="F14" t="n">
-        <v>242.3595009492003</v>
+        <v>55.92</v>
       </c>
       <c r="G14" t="n">
-        <v>242.3595009492003</v>
+        <v>55.92</v>
       </c>
       <c r="H14" t="n">
         <v>55.92</v>
@@ -5272,22 +5272,22 @@
         <v>491.8172603743391</v>
       </c>
       <c r="K14" t="n">
-        <v>1183.827260374339</v>
+        <v>558.6433349472035</v>
       </c>
       <c r="L14" t="n">
-        <v>1875.837260374339</v>
+        <v>911.3332983460685</v>
       </c>
       <c r="M14" t="n">
-        <v>2478.932378751515</v>
+        <v>1514.428416723245</v>
       </c>
       <c r="N14" t="n">
-        <v>2701.769048861339</v>
+        <v>2206.438416723245</v>
       </c>
       <c r="O14" t="n">
-        <v>2720.73867245535</v>
+        <v>2225.408040317255</v>
       </c>
       <c r="P14" t="n">
-        <v>2796</v>
+        <v>2300.669367861905</v>
       </c>
       <c r="Q14" t="n">
         <v>2796</v>
@@ -5296,25 +5296,25 @@
         <v>2796</v>
       </c>
       <c r="S14" t="n">
-        <v>2796</v>
+        <v>2642.677304590449</v>
       </c>
       <c r="T14" t="n">
-        <v>2693.345866380633</v>
+        <v>2642.677304590449</v>
       </c>
       <c r="U14" t="n">
-        <v>2257.811680231841</v>
+        <v>2642.677304590449</v>
       </c>
       <c r="V14" t="n">
-        <v>1841.800544709796</v>
+        <v>2226.666169068405</v>
       </c>
       <c r="W14" t="n">
-        <v>1417.180872001769</v>
+        <v>1802.046496360377</v>
       </c>
       <c r="X14" t="n">
-        <v>1039.11841396069</v>
+        <v>1423.984038319298</v>
       </c>
       <c r="Y14" t="n">
-        <v>742.8381789275522</v>
+        <v>1127.70380328616</v>
       </c>
     </row>
     <row r="15">
@@ -5345,7 +5345,7 @@
         <v>55.92</v>
       </c>
       <c r="I15" t="n">
-        <v>66.46259494869705</v>
+        <v>66.46259494869703</v>
       </c>
       <c r="J15" t="n">
         <v>432.7955102183356</v>
@@ -5354,10 +5354,10 @@
         <v>883.1974353693228</v>
       </c>
       <c r="L15" t="n">
-        <v>1356.867417395279</v>
+        <v>1215.579155455089</v>
       </c>
       <c r="M15" t="n">
-        <v>1514.168559138138</v>
+        <v>1588.700297197948</v>
       </c>
       <c r="N15" t="n">
         <v>1936.374441104197</v>
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>141.3906134665895</v>
+        <v>188.1586494306731</v>
       </c>
       <c r="C16" t="n">
-        <v>141.3906134665895</v>
+        <v>132.8806225134562</v>
       </c>
       <c r="D16" t="n">
-        <v>141.3906134665895</v>
+        <v>64.66222043713753</v>
       </c>
       <c r="E16" t="n">
-        <v>141.3906134665895</v>
+        <v>64.66222043713753</v>
       </c>
       <c r="F16" t="n">
-        <v>141.3906134665895</v>
+        <v>64.66222043713753</v>
       </c>
       <c r="G16" t="n">
-        <v>141.3906134665895</v>
+        <v>64.66222043713753</v>
       </c>
       <c r="H16" t="n">
-        <v>132.648393029452</v>
+        <v>55.92</v>
       </c>
       <c r="I16" t="n">
-        <v>180.6879840966825</v>
+        <v>103.9595910672305</v>
       </c>
       <c r="J16" t="n">
-        <v>378.2523536015927</v>
+        <v>301.5239605721408</v>
       </c>
       <c r="K16" t="n">
-        <v>378.2523536015927</v>
+        <v>301.5239605721408</v>
       </c>
       <c r="L16" t="n">
-        <v>378.2523536015927</v>
+        <v>301.5239605721408</v>
       </c>
       <c r="M16" t="n">
-        <v>378.2523536015927</v>
+        <v>301.5239605721408</v>
       </c>
       <c r="N16" t="n">
-        <v>378.2523536015927</v>
+        <v>301.5239605721408</v>
       </c>
       <c r="O16" t="n">
-        <v>378.2523536015927</v>
+        <v>301.5239605721408</v>
       </c>
       <c r="P16" t="n">
-        <v>378.2523536015927</v>
+        <v>301.5239605721408</v>
       </c>
       <c r="Q16" t="n">
-        <v>378.2523536015927</v>
+        <v>301.5239605721408</v>
       </c>
       <c r="R16" t="n">
-        <v>55.92</v>
+        <v>301.5239605721408</v>
       </c>
       <c r="S16" t="n">
-        <v>55.92</v>
+        <v>272.4080345667589</v>
       </c>
       <c r="T16" t="n">
-        <v>64.82255784732945</v>
+        <v>281.3105924140883</v>
       </c>
       <c r="U16" t="n">
-        <v>131.2066042561079</v>
+        <v>347.6946388228668</v>
       </c>
       <c r="V16" t="n">
-        <v>149.8479971420539</v>
+        <v>366.3360317088127</v>
       </c>
       <c r="W16" t="n">
-        <v>141.3906134665895</v>
+        <v>357.8786480333484</v>
       </c>
       <c r="X16" t="n">
-        <v>141.3906134665895</v>
+        <v>328.1375920433408</v>
       </c>
       <c r="Y16" t="n">
-        <v>141.3906134665895</v>
+        <v>257.9705689630757</v>
       </c>
     </row>
     <row r="17">
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>683.0598760183001</v>
+        <v>676.6964877928162</v>
       </c>
       <c r="C17" t="n">
-        <v>541.1663626415385</v>
+        <v>534.8029744160547</v>
       </c>
       <c r="D17" t="n">
-        <v>438.8035790659327</v>
+        <v>432.4401908404488</v>
       </c>
       <c r="E17" t="n">
-        <v>342.4770239074795</v>
+        <v>336.1136356819957</v>
       </c>
       <c r="F17" t="n">
-        <v>245.6188130913059</v>
+        <v>239.2554248658221</v>
       </c>
       <c r="G17" t="n">
-        <v>150.4403090300084</v>
+        <v>144.0769208045245</v>
       </c>
       <c r="H17" t="n">
         <v>55.92</v>
@@ -5509,22 +5509,22 @@
         <v>491.8172603743391</v>
       </c>
       <c r="K17" t="n">
-        <v>1183.827260374339</v>
+        <v>982.6675830730513</v>
       </c>
       <c r="L17" t="n">
-        <v>1262.727837469411</v>
+        <v>1065.571237746418</v>
       </c>
       <c r="M17" t="n">
-        <v>1865.822955846587</v>
+        <v>1393.010376405989</v>
       </c>
       <c r="N17" t="n">
-        <v>1865.822955846587</v>
+        <v>2085.020376405989</v>
       </c>
       <c r="O17" t="n">
-        <v>1884.792579440598</v>
+        <v>2103.99</v>
       </c>
       <c r="P17" t="n">
-        <v>2576.802579440598</v>
+        <v>2796</v>
       </c>
       <c r="Q17" t="n">
         <v>2796</v>
@@ -5551,7 +5551,7 @@
         <v>1055.804311669969</v>
       </c>
       <c r="Y17" t="n">
-        <v>857.8066567815067</v>
+        <v>851.4432685560228</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>250.0892163925362</v>
+        <v>395.1956854557947</v>
       </c>
       <c r="C18" t="n">
-        <v>197.463042205143</v>
+        <v>342.5695112684015</v>
       </c>
       <c r="D18" t="n">
-        <v>158.1320453387767</v>
+        <v>303.2385144020352</v>
       </c>
       <c r="E18" t="n">
-        <v>124.1198259227033</v>
+        <v>269.2262949859618</v>
       </c>
       <c r="F18" t="n">
         <v>93.17412659151456</v>
@@ -5606,31 +5606,31 @@
         <v>1609.207680368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>1609.207680368536</v>
+        <v>1470.988944904548</v>
       </c>
       <c r="R18" t="n">
-        <v>1386.333366351076</v>
+        <v>1248.114630887089</v>
       </c>
       <c r="S18" t="n">
-        <v>1232.504854856424</v>
+        <v>1094.286119392436</v>
       </c>
       <c r="T18" t="n">
-        <v>1136.329753721905</v>
+        <v>998.111018257917</v>
       </c>
       <c r="U18" t="n">
-        <v>1044.216945120992</v>
+        <v>905.9982096570041</v>
       </c>
       <c r="V18" t="n">
-        <v>937.640513614406</v>
+        <v>799.421778150418</v>
       </c>
       <c r="W18" t="n">
-        <v>813.021177341852</v>
+        <v>674.802441877864</v>
       </c>
       <c r="X18" t="n">
-        <v>701.0386122455009</v>
+        <v>562.8198767815129</v>
       </c>
       <c r="Y18" t="n">
-        <v>609.7341751079914</v>
+        <v>471.5154396440034</v>
       </c>
     </row>
     <row r="19">
@@ -5670,25 +5670,25 @@
         <v>1345.508265270047</v>
       </c>
       <c r="L19" t="n">
-        <v>1265.550038450631</v>
+        <v>1345.508265270047</v>
       </c>
       <c r="M19" t="n">
-        <v>1089.47035148995</v>
+        <v>1345.508265270047</v>
       </c>
       <c r="N19" t="n">
-        <v>861.430384747562</v>
+        <v>1345.508265270047</v>
       </c>
       <c r="O19" t="n">
-        <v>560.6215851314018</v>
+        <v>1221.036655006402</v>
       </c>
       <c r="P19" t="n">
-        <v>560.6215851314018</v>
+        <v>867.8458330652707</v>
       </c>
       <c r="Q19" t="n">
-        <v>159.7051543984746</v>
+        <v>466.9294023323434</v>
       </c>
       <c r="R19" t="n">
-        <v>105.6424418260338</v>
+        <v>55.92</v>
       </c>
       <c r="S19" t="n">
         <v>55.92</v>
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>683.1398760183001</v>
+        <v>680.6964877928162</v>
       </c>
       <c r="C20" t="n">
-        <v>541.2463626415386</v>
+        <v>538.8029744160547</v>
       </c>
       <c r="D20" t="n">
-        <v>438.8835790659327</v>
+        <v>436.4401908404488</v>
       </c>
       <c r="E20" t="n">
-        <v>342.5570239074795</v>
+        <v>340.1136356819957</v>
       </c>
       <c r="F20" t="n">
-        <v>245.6988130913059</v>
+        <v>243.2554248658221</v>
       </c>
       <c r="G20" t="n">
-        <v>150.5203090300084</v>
+        <v>148.0769208045246</v>
       </c>
       <c r="H20" t="n">
         <v>56</v>
@@ -5743,22 +5743,22 @@
         <v>56</v>
       </c>
       <c r="J20" t="n">
-        <v>491.8972603743391</v>
+        <v>65.89557115404399</v>
       </c>
       <c r="K20" t="n">
-        <v>558.7233349472034</v>
+        <v>221.3432983460685</v>
       </c>
       <c r="L20" t="n">
-        <v>918.6693678619054</v>
+        <v>914.3432983460685</v>
       </c>
       <c r="M20" t="n">
-        <v>918.6693678619054</v>
+        <v>1517.438416723245</v>
       </c>
       <c r="N20" t="n">
-        <v>918.6693678619054</v>
+        <v>2210.438416723245</v>
       </c>
       <c r="O20" t="n">
-        <v>1611.669367861905</v>
+        <v>2229.408040317255</v>
       </c>
       <c r="P20" t="n">
         <v>2304.669367861905</v>
@@ -5776,19 +5776,19 @@
         <v>2346.354996413144</v>
       </c>
       <c r="U20" t="n">
-        <v>2005.183390409028</v>
+        <v>2002.740002183544</v>
       </c>
       <c r="V20" t="n">
-        <v>1681.091446806175</v>
+        <v>1678.648058580691</v>
       </c>
       <c r="W20" t="n">
-        <v>1348.390966017339</v>
+        <v>1345.947577791855</v>
       </c>
       <c r="X20" t="n">
-        <v>1062.247699895453</v>
+        <v>1059.804311669969</v>
       </c>
       <c r="Y20" t="n">
-        <v>857.8866567815066</v>
+        <v>855.4432685560228</v>
       </c>
     </row>
     <row r="21">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>250.1692163925362</v>
+        <v>533.4944209197827</v>
       </c>
       <c r="C21" t="n">
         <v>197.543042205143</v>
@@ -5813,7 +5813,7 @@
         <v>93.25412659151456</v>
       </c>
       <c r="G21" t="n">
-        <v>76.63229694835753</v>
+        <v>76.63229694835755</v>
       </c>
       <c r="H21" t="n">
         <v>56</v>
@@ -5849,25 +5849,25 @@
         <v>1386.413366351076</v>
       </c>
       <c r="S21" t="n">
-        <v>949.2596503291778</v>
+        <v>1232.584854856424</v>
       </c>
       <c r="T21" t="n">
-        <v>853.0845491946584</v>
+        <v>1136.409753721905</v>
       </c>
       <c r="U21" t="n">
-        <v>760.9717405937455</v>
+        <v>1044.296945120992</v>
       </c>
       <c r="V21" t="n">
-        <v>654.3953090871595</v>
+        <v>937.7205136144059</v>
       </c>
       <c r="W21" t="n">
-        <v>529.7759728146054</v>
+        <v>813.1011773418519</v>
       </c>
       <c r="X21" t="n">
-        <v>417.7934077182543</v>
+        <v>701.1186122455008</v>
       </c>
       <c r="Y21" t="n">
-        <v>326.4889705807449</v>
+        <v>609.8141751079913</v>
       </c>
     </row>
     <row r="22">
@@ -5916,10 +5916,10 @@
         <v>1345.588265270047</v>
       </c>
       <c r="O22" t="n">
-        <v>1221.116655006402</v>
+        <v>1044.779465653887</v>
       </c>
       <c r="P22" t="n">
-        <v>867.9258330652706</v>
+        <v>691.5886437127554</v>
       </c>
       <c r="Q22" t="n">
         <v>467.0094023323434</v>
@@ -5956,16 +5956,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>683.1398760183</v>
+        <v>683.1398760183001</v>
       </c>
       <c r="C23" t="n">
-        <v>541.2463626415384</v>
+        <v>541.2463626415386</v>
       </c>
       <c r="D23" t="n">
-        <v>438.8835790659326</v>
+        <v>438.8835790659327</v>
       </c>
       <c r="E23" t="n">
-        <v>342.5570239074794</v>
+        <v>342.5570239074795</v>
       </c>
       <c r="F23" t="n">
         <v>245.6988130913059</v>
@@ -5983,16 +5983,16 @@
         <v>491.8972603743391</v>
       </c>
       <c r="K23" t="n">
-        <v>1180.722507696035</v>
+        <v>1180.722507696118</v>
       </c>
       <c r="L23" t="n">
-        <v>1263.626162369402</v>
+        <v>1263.626162369485</v>
       </c>
       <c r="M23" t="n">
-        <v>1866.721280746578</v>
+        <v>1866.721280746661</v>
       </c>
       <c r="N23" t="n">
-        <v>2210.438416723245</v>
+        <v>1866.721280746661</v>
       </c>
       <c r="O23" t="n">
         <v>2229.408040317255</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>533.4944209197827</v>
+        <v>250.1692163925362</v>
       </c>
       <c r="C24" t="n">
-        <v>480.8682467323894</v>
+        <v>197.543042205143</v>
       </c>
       <c r="D24" t="n">
-        <v>441.5372498660231</v>
+        <v>158.2120453387767</v>
       </c>
       <c r="E24" t="n">
-        <v>407.5250304499497</v>
+        <v>124.1998259227033</v>
       </c>
       <c r="F24" t="n">
-        <v>376.579331118761</v>
+        <v>93.25412659151456</v>
       </c>
       <c r="G24" t="n">
-        <v>359.957501475604</v>
+        <v>76.63229694835753</v>
       </c>
       <c r="H24" t="n">
         <v>56</v>
@@ -6092,19 +6092,19 @@
         <v>1136.409753721905</v>
       </c>
       <c r="U24" t="n">
-        <v>1044.296945120992</v>
+        <v>760.9717405937455</v>
       </c>
       <c r="V24" t="n">
-        <v>937.7205136144059</v>
+        <v>654.3953090871595</v>
       </c>
       <c r="W24" t="n">
-        <v>813.1011773418519</v>
+        <v>529.7759728146054</v>
       </c>
       <c r="X24" t="n">
-        <v>701.1186122455008</v>
+        <v>417.7934077182543</v>
       </c>
       <c r="Y24" t="n">
-        <v>609.8141751079913</v>
+        <v>326.4889705807449</v>
       </c>
     </row>
     <row r="25">
@@ -6156,7 +6156,7 @@
         <v>1221.116655006402</v>
       </c>
       <c r="P25" t="n">
-        <v>867.9258330652707</v>
+        <v>867.9258330652706</v>
       </c>
       <c r="Q25" t="n">
         <v>467.0094023323434</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.68</v>
+        <v>722.9636502688952</v>
       </c>
       <c r="C26" t="n">
-        <v>31.68</v>
+        <v>513.393369215366</v>
       </c>
       <c r="D26" t="n">
-        <v>31.68</v>
+        <v>357.880399541997</v>
       </c>
       <c r="E26" t="n">
-        <v>31.68</v>
+        <v>193.8770767067761</v>
       </c>
       <c r="F26" t="n">
-        <v>31.68</v>
+        <v>193.8770767067761</v>
       </c>
       <c r="G26" t="n">
-        <v>31.68</v>
+        <v>193.8770767067761</v>
       </c>
       <c r="H26" t="n">
         <v>31.68</v>
@@ -6217,22 +6217,22 @@
         <v>31.68</v>
       </c>
       <c r="J26" t="n">
-        <v>239.1806471597586</v>
+        <v>41.57557115404399</v>
       </c>
       <c r="K26" t="n">
-        <v>306.0067217326229</v>
+        <v>108.4016457269083</v>
       </c>
       <c r="L26" t="n">
-        <v>388.9103764059898</v>
+        <v>313.6490488613398</v>
       </c>
       <c r="M26" t="n">
-        <v>388.9103764059898</v>
+        <v>705.6890488613399</v>
       </c>
       <c r="N26" t="n">
-        <v>780.9503764059898</v>
+        <v>1097.72904886134</v>
       </c>
       <c r="O26" t="n">
-        <v>799.9200000000001</v>
+        <v>1116.69867245535</v>
       </c>
       <c r="P26" t="n">
         <v>1191.96</v>
@@ -6244,25 +6244,25 @@
         <v>1584</v>
       </c>
       <c r="S26" t="n">
-        <v>1584</v>
+        <v>1340.812215660818</v>
       </c>
       <c r="T26" t="n">
-        <v>1584</v>
+        <v>995.0014610596087</v>
       </c>
       <c r="U26" t="n">
-        <v>1183.999999999997</v>
+        <v>995.0014610596087</v>
       </c>
       <c r="V26" t="n">
-        <v>792.2312887203772</v>
+        <v>995.0014610596087</v>
       </c>
       <c r="W26" t="n">
-        <v>392.2312887203747</v>
+        <v>995.0014610596087</v>
       </c>
       <c r="X26" t="n">
-        <v>303.7178107907135</v>
+        <v>995.0014610596087</v>
       </c>
       <c r="Y26" t="n">
-        <v>31.68</v>
+        <v>722.9636502688952</v>
       </c>
     </row>
     <row r="27">
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>511.6068805889814</v>
+        <v>412.984413581025</v>
       </c>
       <c r="C27" t="n">
-        <v>511.6068805889814</v>
+        <v>412.984413581025</v>
       </c>
       <c r="D27" t="n">
-        <v>404.5991160458474</v>
+        <v>305.976649037891</v>
       </c>
       <c r="E27" t="n">
-        <v>302.9101289530064</v>
+        <v>204.2876619450499</v>
       </c>
       <c r="F27" t="n">
         <v>204.2876619450499</v>
@@ -6293,22 +6293,22 @@
         <v>31.68</v>
       </c>
       <c r="I27" t="n">
-        <v>31.67999999999984</v>
+        <v>31.68</v>
       </c>
       <c r="J27" t="n">
-        <v>182.1929152696384</v>
+        <v>182.1929152696386</v>
       </c>
       <c r="K27" t="n">
-        <v>416.7748404206256</v>
+        <v>415.8071600520902</v>
       </c>
       <c r="L27" t="n">
-        <v>749.1565605063918</v>
+        <v>748.1888801378564</v>
       </c>
       <c r="M27" t="n">
-        <v>906.457702249251</v>
+        <v>905.4900218807156</v>
       </c>
       <c r="N27" t="n">
-        <v>1112.84358421531</v>
+        <v>1111.875903846774</v>
       </c>
       <c r="O27" t="n">
         <v>1417.795694775776</v>
@@ -6320,28 +6320,28 @@
         <v>1584</v>
       </c>
       <c r="R27" t="n">
-        <v>1584</v>
+        <v>1483.676055337493</v>
       </c>
       <c r="S27" t="n">
-        <v>1362.49472082858</v>
+        <v>1262.170776166073</v>
       </c>
       <c r="T27" t="n">
-        <v>1362.49472082858</v>
+        <v>1262.170776166073</v>
       </c>
       <c r="U27" t="n">
-        <v>1202.7051445509</v>
+        <v>1262.170776166073</v>
       </c>
       <c r="V27" t="n">
-        <v>1186.540043990675</v>
+        <v>1087.917576982719</v>
       </c>
       <c r="W27" t="n">
-        <v>994.2439400413538</v>
+        <v>895.6214730333973</v>
       </c>
       <c r="X27" t="n">
-        <v>814.584607268235</v>
+        <v>715.9621402602785</v>
       </c>
       <c r="Y27" t="n">
-        <v>655.6034024539579</v>
+        <v>556.9809354460014</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>212.3589154017313</v>
+        <v>178.7761873821198</v>
       </c>
       <c r="C28" t="n">
-        <v>212.3589154017313</v>
+        <v>147.7405847073272</v>
       </c>
       <c r="D28" t="n">
-        <v>212.3589154017313</v>
+        <v>103.7646068734328</v>
       </c>
       <c r="E28" t="n">
-        <v>212.3589154017313</v>
+        <v>64.38995552297165</v>
       </c>
       <c r="F28" t="n">
-        <v>212.3589154017313</v>
+        <v>31.68</v>
       </c>
       <c r="G28" t="n">
-        <v>212.3589154017313</v>
+        <v>31.68</v>
       </c>
       <c r="H28" t="n">
-        <v>227.5506651512928</v>
+        <v>46.8717497495615</v>
       </c>
       <c r="I28" t="n">
-        <v>299.3502562185232</v>
+        <v>118.671340816792</v>
       </c>
       <c r="J28" t="n">
-        <v>520.6746257234336</v>
+        <v>339.9957103217023</v>
       </c>
       <c r="K28" t="n">
-        <v>520.6746257234336</v>
+        <v>339.9957103217023</v>
       </c>
       <c r="L28" t="n">
-        <v>520.6746257234336</v>
+        <v>339.9957103217023</v>
       </c>
       <c r="M28" t="n">
-        <v>520.6746257234336</v>
+        <v>339.9957103217023</v>
       </c>
       <c r="N28" t="n">
-        <v>520.6746257234336</v>
+        <v>339.9957103217023</v>
       </c>
       <c r="O28" t="n">
-        <v>520.6746257234336</v>
+        <v>339.9957103217023</v>
       </c>
       <c r="P28" t="n">
-        <v>431.68</v>
+        <v>339.9957103217023</v>
       </c>
       <c r="Q28" t="n">
-        <v>31.68</v>
+        <v>339.9957103217023</v>
       </c>
       <c r="R28" t="n">
-        <v>31.68</v>
+        <v>206.9905756110093</v>
       </c>
       <c r="S28" t="n">
-        <v>31.68</v>
+        <v>89.59136610820781</v>
       </c>
       <c r="T28" t="n">
-        <v>64.34255784732946</v>
+        <v>122.2539239555373</v>
       </c>
       <c r="U28" t="n">
-        <v>154.4866042561079</v>
+        <v>212.3979703643157</v>
       </c>
       <c r="V28" t="n">
-        <v>196.8879971420539</v>
+        <v>254.7993632502617</v>
       </c>
       <c r="W28" t="n">
-        <v>212.3589154017313</v>
+        <v>270.2702815099391</v>
       </c>
       <c r="X28" t="n">
-        <v>212.3589154017313</v>
+        <v>270.2702815099391</v>
       </c>
       <c r="Y28" t="n">
-        <v>212.3589154017313</v>
+        <v>224.3456826720983</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>995.0014610596087</v>
+        <v>738.0218875056202</v>
       </c>
       <c r="C29" t="n">
-        <v>785.4311800060794</v>
+        <v>528.4516064520909</v>
       </c>
       <c r="D29" t="n">
-        <v>685.2706497730035</v>
+        <v>358.4120551997174</v>
       </c>
       <c r="E29" t="n">
-        <v>521.2673269377826</v>
+        <v>358.4120551997174</v>
       </c>
       <c r="F29" t="n">
-        <v>356.7323484448414</v>
+        <v>193.8770767067761</v>
       </c>
       <c r="G29" t="n">
         <v>193.8770767067761</v>
@@ -6454,19 +6454,19 @@
         <v>31.68</v>
       </c>
       <c r="J29" t="n">
-        <v>163.9193196151087</v>
+        <v>423.72</v>
       </c>
       <c r="K29" t="n">
-        <v>230.745394187973</v>
+        <v>490.5460745728644</v>
       </c>
       <c r="L29" t="n">
-        <v>313.6490488613398</v>
+        <v>573.4497292462312</v>
       </c>
       <c r="M29" t="n">
-        <v>705.6890488613399</v>
+        <v>573.4497292462312</v>
       </c>
       <c r="N29" t="n">
-        <v>1097.72904886134</v>
+        <v>724.6586724553501</v>
       </c>
       <c r="O29" t="n">
         <v>1116.69867245535</v>
@@ -6484,22 +6484,22 @@
         <v>1340.812215660818</v>
       </c>
       <c r="T29" t="n">
-        <v>995.0014610596087</v>
+        <v>1252.483246736308</v>
       </c>
       <c r="U29" t="n">
-        <v>995.0014610596087</v>
+        <v>1252.483246736308</v>
       </c>
       <c r="V29" t="n">
-        <v>995.0014610596087</v>
+        <v>1252.483246736308</v>
       </c>
       <c r="W29" t="n">
-        <v>995.0014610596087</v>
+        <v>1252.483246736308</v>
       </c>
       <c r="X29" t="n">
-        <v>995.0014610596087</v>
+        <v>1252.483246736308</v>
       </c>
       <c r="Y29" t="n">
-        <v>995.0014610596087</v>
+        <v>980.4454359455945</v>
       </c>
     </row>
     <row r="30">
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>631.9098224531424</v>
+        <v>511.6068805889814</v>
       </c>
       <c r="C30" t="n">
         <v>511.6068805889814</v>
@@ -6530,22 +6530,22 @@
         <v>31.68</v>
       </c>
       <c r="I30" t="n">
-        <v>31.67999999999984</v>
+        <v>31.68</v>
       </c>
       <c r="J30" t="n">
-        <v>182.1929152696384</v>
+        <v>182.1929152696386</v>
       </c>
       <c r="K30" t="n">
-        <v>415.8071600520902</v>
+        <v>416.7748404206258</v>
       </c>
       <c r="L30" t="n">
-        <v>748.1888801378564</v>
+        <v>749.156560506392</v>
       </c>
       <c r="M30" t="n">
-        <v>905.4900218807156</v>
+        <v>906.4577022492513</v>
       </c>
       <c r="N30" t="n">
-        <v>1111.875903846774</v>
+        <v>1112.84358421531</v>
       </c>
       <c r="O30" t="n">
         <v>1417.795694775776</v>
@@ -6557,28 +6557,28 @@
         <v>1584</v>
       </c>
       <c r="R30" t="n">
-        <v>1293.448918305773</v>
+        <v>1408.045323162095</v>
       </c>
       <c r="S30" t="n">
-        <v>1293.448918305773</v>
+        <v>1186.540043990675</v>
       </c>
       <c r="T30" t="n">
-        <v>1129.597049494486</v>
+        <v>1186.540043990675</v>
       </c>
       <c r="U30" t="n">
-        <v>969.8074732168051</v>
+        <v>1186.540043990675</v>
       </c>
       <c r="V30" t="n">
-        <v>795.5542740334514</v>
+        <v>1186.540043990675</v>
       </c>
       <c r="W30" t="n">
-        <v>790.8910272674195</v>
+        <v>994.2439400413538</v>
       </c>
       <c r="X30" t="n">
-        <v>790.8910272674195</v>
+        <v>814.584607268235</v>
       </c>
       <c r="Y30" t="n">
-        <v>631.9098224531424</v>
+        <v>655.6034024539579</v>
       </c>
     </row>
     <row r="31">
@@ -6624,25 +6624,25 @@
         <v>520.6746257234336</v>
       </c>
       <c r="N31" t="n">
-        <v>520.6746257234336</v>
+        <v>224.9578913042784</v>
       </c>
       <c r="O31" t="n">
-        <v>520.6746257234336</v>
+        <v>31.68</v>
       </c>
       <c r="P31" t="n">
-        <v>520.6746257234336</v>
+        <v>31.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>520.6746257234336</v>
+        <v>31.68</v>
       </c>
       <c r="R31" t="n">
-        <v>120.6746257234336</v>
+        <v>31.68</v>
       </c>
       <c r="S31" t="n">
         <v>31.68</v>
       </c>
       <c r="T31" t="n">
-        <v>64.34255784732946</v>
+        <v>64.34255784732945</v>
       </c>
       <c r="U31" t="n">
         <v>154.4866042561079</v>
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>575.2931551411236</v>
+        <v>31.68</v>
       </c>
       <c r="C32" t="n">
-        <v>365.7228740875944</v>
+        <v>31.68</v>
       </c>
       <c r="D32" t="n">
-        <v>195.6833228352209</v>
+        <v>31.68</v>
       </c>
       <c r="E32" t="n">
         <v>31.68</v>
@@ -6694,22 +6694,22 @@
         <v>41.57557115404399</v>
       </c>
       <c r="K32" t="n">
-        <v>433.6155711540439</v>
+        <v>230.745394187973</v>
       </c>
       <c r="L32" t="n">
-        <v>516.5192258274108</v>
+        <v>313.6490488613398</v>
       </c>
       <c r="M32" t="n">
-        <v>908.559225827411</v>
+        <v>705.6890488613399</v>
       </c>
       <c r="N32" t="n">
-        <v>1300.599225827411</v>
+        <v>1097.72904886134</v>
       </c>
       <c r="O32" t="n">
-        <v>1319.568849421421</v>
+        <v>1116.69867245535</v>
       </c>
       <c r="P32" t="n">
-        <v>1394.830176966071</v>
+        <v>1191.96</v>
       </c>
       <c r="Q32" t="n">
         <v>1584</v>
@@ -6724,19 +6724,19 @@
         <v>1584</v>
       </c>
       <c r="U32" t="n">
-        <v>1584</v>
+        <v>1183.999999999998</v>
       </c>
       <c r="V32" t="n">
-        <v>1584</v>
+        <v>792.2312887203778</v>
       </c>
       <c r="W32" t="n">
-        <v>1443.574548170466</v>
+        <v>392.231288720378</v>
       </c>
       <c r="X32" t="n">
-        <v>1089.754514371811</v>
+        <v>303.7178107907135</v>
       </c>
       <c r="Y32" t="n">
-        <v>817.7167035810979</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="33">
@@ -6746,19 +6746,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>236.2815391840856</v>
+        <v>459.3021605080924</v>
       </c>
       <c r="C33" t="n">
-        <v>115.9785973199247</v>
+        <v>338.9992186439314</v>
       </c>
       <c r="D33" t="n">
-        <v>115.9785973199247</v>
+        <v>231.9914541007975</v>
       </c>
       <c r="E33" t="n">
-        <v>115.9785973199247</v>
+        <v>130.3024670079564</v>
       </c>
       <c r="F33" t="n">
-        <v>115.9785973199247</v>
+        <v>31.68</v>
       </c>
       <c r="G33" t="n">
         <v>31.68</v>
@@ -6767,19 +6767,19 @@
         <v>31.68</v>
       </c>
       <c r="I33" t="n">
-        <v>31.67999999999984</v>
+        <v>31.68</v>
       </c>
       <c r="J33" t="n">
-        <v>182.1929152696384</v>
+        <v>182.1929152696386</v>
       </c>
       <c r="K33" t="n">
-        <v>416.7748404206256</v>
+        <v>416.7748404206258</v>
       </c>
       <c r="L33" t="n">
-        <v>749.1565605063918</v>
+        <v>749.156560506392</v>
       </c>
       <c r="M33" t="n">
-        <v>906.457702249251</v>
+        <v>905.4900218807156</v>
       </c>
       <c r="N33" t="n">
         <v>1111.875903846774</v>
@@ -6794,28 +6794,28 @@
         <v>1584</v>
       </c>
       <c r="R33" t="n">
-        <v>1409.109346858101</v>
+        <v>1584</v>
       </c>
       <c r="S33" t="n">
-        <v>1409.109346858101</v>
+        <v>1439.833864232786</v>
       </c>
       <c r="T33" t="n">
-        <v>1245.257478046814</v>
+        <v>1275.981995421499</v>
       </c>
       <c r="U33" t="n">
-        <v>1085.467901769133</v>
+        <v>1116.192419143818</v>
       </c>
       <c r="V33" t="n">
-        <v>911.2147025857796</v>
+        <v>941.9392199604646</v>
       </c>
       <c r="W33" t="n">
-        <v>718.9185986364579</v>
+        <v>941.9392199604646</v>
       </c>
       <c r="X33" t="n">
-        <v>539.2592658633391</v>
+        <v>762.2798871873458</v>
       </c>
       <c r="Y33" t="n">
-        <v>380.278061049062</v>
+        <v>603.2986823730687</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>146.0662318591482</v>
+        <v>212.3589154017313</v>
       </c>
       <c r="C34" t="n">
-        <v>115.0306291843556</v>
+        <v>212.3589154017313</v>
       </c>
       <c r="D34" t="n">
-        <v>71.05465135046116</v>
+        <v>212.3589154017313</v>
       </c>
       <c r="E34" t="n">
+        <v>212.3589154017313</v>
+      </c>
+      <c r="F34" t="n">
+        <v>212.3589154017313</v>
+      </c>
+      <c r="G34" t="n">
+        <v>212.3589154017313</v>
+      </c>
+      <c r="H34" t="n">
+        <v>227.5506651512928</v>
+      </c>
+      <c r="I34" t="n">
+        <v>299.3502562185232</v>
+      </c>
+      <c r="J34" t="n">
+        <v>520.6746257234336</v>
+      </c>
+      <c r="K34" t="n">
+        <v>520.6746257234336</v>
+      </c>
+      <c r="L34" t="n">
+        <v>520.6746257234336</v>
+      </c>
+      <c r="M34" t="n">
+        <v>520.6746257234336</v>
+      </c>
+      <c r="N34" t="n">
+        <v>520.6746257234336</v>
+      </c>
+      <c r="O34" t="n">
+        <v>520.6746257234336</v>
+      </c>
+      <c r="P34" t="n">
+        <v>520.6746257234336</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>431.68</v>
+      </c>
+      <c r="R34" t="n">
         <v>31.68</v>
       </c>
-      <c r="F34" t="n">
+      <c r="S34" t="n">
         <v>31.68</v>
       </c>
-      <c r="G34" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="H34" t="n">
-        <v>46.8717497495615</v>
-      </c>
-      <c r="I34" t="n">
-        <v>118.671340816792</v>
-      </c>
-      <c r="J34" t="n">
-        <v>339.9957103217023</v>
-      </c>
-      <c r="K34" t="n">
-        <v>339.9957103217023</v>
-      </c>
-      <c r="L34" t="n">
-        <v>339.9957103217023</v>
-      </c>
-      <c r="M34" t="n">
-        <v>339.9957103217023</v>
-      </c>
-      <c r="N34" t="n">
-        <v>339.9957103217023</v>
-      </c>
-      <c r="O34" t="n">
-        <v>339.9957103217023</v>
-      </c>
-      <c r="P34" t="n">
-        <v>339.9957103217023</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>339.9957103217023</v>
-      </c>
-      <c r="R34" t="n">
-        <v>174.2806200880377</v>
-      </c>
-      <c r="S34" t="n">
-        <v>56.88141058523615</v>
-      </c>
       <c r="T34" t="n">
-        <v>89.54396843256561</v>
+        <v>64.34255784732946</v>
       </c>
       <c r="U34" t="n">
-        <v>179.6880148413441</v>
+        <v>154.4866042561079</v>
       </c>
       <c r="V34" t="n">
-        <v>222.08940772729</v>
+        <v>196.8879971420539</v>
       </c>
       <c r="W34" t="n">
-        <v>237.5603259869674</v>
+        <v>212.3589154017313</v>
       </c>
       <c r="X34" t="n">
-        <v>237.5603259869674</v>
+        <v>212.3589154017313</v>
       </c>
       <c r="Y34" t="n">
-        <v>191.6357271491266</v>
+        <v>212.3589154017313</v>
       </c>
     </row>
     <row r="35">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>193.8770767067761</v>
+        <v>31.68</v>
       </c>
       <c r="C35" t="n">
-        <v>193.8770767067761</v>
+        <v>31.68</v>
       </c>
       <c r="D35" t="n">
-        <v>193.8770767067761</v>
+        <v>31.68</v>
       </c>
       <c r="E35" t="n">
-        <v>193.8770767067761</v>
+        <v>31.68</v>
       </c>
       <c r="F35" t="n">
-        <v>193.8770767067761</v>
+        <v>31.68</v>
       </c>
       <c r="G35" t="n">
-        <v>193.8770767067761</v>
+        <v>31.68</v>
       </c>
       <c r="H35" t="n">
         <v>31.68</v>
@@ -6928,25 +6928,25 @@
         <v>31.68</v>
       </c>
       <c r="J35" t="n">
-        <v>41.57557115404399</v>
+        <v>423.72</v>
       </c>
       <c r="K35" t="n">
-        <v>249.7150177819832</v>
+        <v>622.7853941879731</v>
       </c>
       <c r="L35" t="n">
-        <v>332.6186724553501</v>
+        <v>705.6890488613399</v>
       </c>
       <c r="M35" t="n">
-        <v>724.6586724553501</v>
+        <v>1097.72904886134</v>
       </c>
       <c r="N35" t="n">
-        <v>724.6586724553501</v>
+        <v>1489.76904886134</v>
       </c>
       <c r="O35" t="n">
-        <v>1116.69867245535</v>
+        <v>1508.73867245535</v>
       </c>
       <c r="P35" t="n">
-        <v>1191.96</v>
+        <v>1584</v>
       </c>
       <c r="Q35" t="n">
         <v>1584</v>
@@ -6955,25 +6955,25 @@
         <v>1584</v>
       </c>
       <c r="S35" t="n">
-        <v>1340.812215660818</v>
+        <v>1584</v>
       </c>
       <c r="T35" t="n">
-        <v>1340.812215660818</v>
+        <v>1449.306555868988</v>
       </c>
       <c r="U35" t="n">
-        <v>947.6971105054329</v>
+        <v>1449.306555868988</v>
       </c>
       <c r="V35" t="n">
-        <v>947.6971105054329</v>
+        <v>1057.537844589368</v>
       </c>
       <c r="W35" t="n">
-        <v>547.6971105054304</v>
+        <v>657.5378445893678</v>
       </c>
       <c r="X35" t="n">
-        <v>193.8770767067761</v>
+        <v>303.7178107907135</v>
       </c>
       <c r="Y35" t="n">
-        <v>193.8770767067761</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="36">
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>119.9890646251252</v>
+        <v>547.6112251332177</v>
       </c>
       <c r="C36" t="n">
-        <v>119.9890646251252</v>
+        <v>427.3082832690567</v>
       </c>
       <c r="D36" t="n">
-        <v>119.9890646251252</v>
+        <v>320.3005187259227</v>
       </c>
       <c r="E36" t="n">
-        <v>119.9890646251252</v>
+        <v>218.6115316330817</v>
       </c>
       <c r="F36" t="n">
         <v>119.9890646251252</v>
@@ -7019,7 +7019,7 @@
         <v>906.4577022492513</v>
       </c>
       <c r="N36" t="n">
-        <v>1111.875903846774</v>
+        <v>1112.84358421531</v>
       </c>
       <c r="O36" t="n">
         <v>1417.795694775776</v>
@@ -7031,28 +7031,28 @@
         <v>1584</v>
       </c>
       <c r="R36" t="n">
-        <v>1293.448918305773</v>
+        <v>1584</v>
       </c>
       <c r="S36" t="n">
-        <v>1071.943639134353</v>
+        <v>1528.142928857911</v>
       </c>
       <c r="T36" t="n">
-        <v>908.0917703230656</v>
+        <v>1364.291060046624</v>
       </c>
       <c r="U36" t="n">
-        <v>748.302194045385</v>
+        <v>1204.501483768943</v>
       </c>
       <c r="V36" t="n">
-        <v>574.0489948620313</v>
+        <v>1030.24828458559</v>
       </c>
       <c r="W36" t="n">
-        <v>458.6296022125211</v>
+        <v>1030.24828458559</v>
       </c>
       <c r="X36" t="n">
-        <v>278.9702694394024</v>
+        <v>850.5889518124711</v>
       </c>
       <c r="Y36" t="n">
-        <v>119.9890646251252</v>
+        <v>691.607746998194</v>
       </c>
     </row>
     <row r="37">
@@ -7095,10 +7095,10 @@
         <v>520.6746257234336</v>
       </c>
       <c r="M37" t="n">
-        <v>520.6746257234336</v>
+        <v>327.3967344191552</v>
       </c>
       <c r="N37" t="n">
-        <v>400.1655672929278</v>
+        <v>31.68</v>
       </c>
       <c r="O37" t="n">
         <v>31.68</v>
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.68</v>
+        <v>941.5764515600237</v>
       </c>
       <c r="C38" t="n">
-        <v>31.68</v>
+        <v>732.0061705064944</v>
       </c>
       <c r="D38" t="n">
-        <v>31.68</v>
+        <v>561.9666192541208</v>
       </c>
       <c r="E38" t="n">
-        <v>31.68</v>
+        <v>397.9632964189</v>
       </c>
       <c r="F38" t="n">
-        <v>31.68</v>
+        <v>233.4283179259587</v>
       </c>
       <c r="G38" t="n">
-        <v>31.68</v>
+        <v>193.8770767067761</v>
       </c>
       <c r="H38" t="n">
         <v>31.68</v>
@@ -7165,19 +7165,19 @@
         <v>31.68</v>
       </c>
       <c r="J38" t="n">
-        <v>41.57557115404399</v>
+        <v>423.72</v>
       </c>
       <c r="K38" t="n">
-        <v>108.4016457269083</v>
+        <v>490.5460745728644</v>
       </c>
       <c r="L38" t="n">
-        <v>191.3053004002752</v>
+        <v>705.6890488613399</v>
       </c>
       <c r="M38" t="n">
-        <v>583.3453004002752</v>
+        <v>705.6890488613399</v>
       </c>
       <c r="N38" t="n">
-        <v>975.3853004002751</v>
+        <v>1097.72904886134</v>
       </c>
       <c r="O38" t="n">
         <v>1116.69867245535</v>
@@ -7195,22 +7195,22 @@
         <v>1584</v>
       </c>
       <c r="T38" t="n">
-        <v>1238.189245398791</v>
+        <v>1584</v>
       </c>
       <c r="U38" t="n">
-        <v>1095.486522070335</v>
+        <v>1183.999999999998</v>
       </c>
       <c r="V38" t="n">
-        <v>703.717810790715</v>
+        <v>1183.999999999998</v>
       </c>
       <c r="W38" t="n">
-        <v>303.7178107907135</v>
+        <v>1183.999999999998</v>
       </c>
       <c r="X38" t="n">
-        <v>303.7178107907135</v>
+        <v>1183.999999999998</v>
       </c>
       <c r="Y38" t="n">
-        <v>31.68</v>
+        <v>1183.999999999998</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>603.4682962753066</v>
+        <v>459.3021605080924</v>
       </c>
       <c r="C39" t="n">
-        <v>483.1653544111456</v>
+        <v>338.9992186439314</v>
       </c>
       <c r="D39" t="n">
-        <v>376.1575898680117</v>
+        <v>231.9914541007975</v>
       </c>
       <c r="E39" t="n">
-        <v>274.4686027751706</v>
+        <v>130.3024670079564</v>
       </c>
       <c r="F39" t="n">
-        <v>175.8461357672142</v>
+        <v>31.68</v>
       </c>
       <c r="G39" t="n">
-        <v>91.54753844728947</v>
+        <v>31.68</v>
       </c>
       <c r="H39" t="n">
         <v>31.68</v>
@@ -7247,7 +7247,7 @@
         <v>182.1929152696386</v>
       </c>
       <c r="K39" t="n">
-        <v>416.7748404206258</v>
+        <v>415.8071600520902</v>
       </c>
       <c r="L39" t="n">
         <v>748.1888801378564</v>
@@ -7268,28 +7268,28 @@
         <v>1584</v>
       </c>
       <c r="R39" t="n">
-        <v>1584</v>
+        <v>1439.833864232786</v>
       </c>
       <c r="S39" t="n">
-        <v>1584</v>
+        <v>1439.833864232786</v>
       </c>
       <c r="T39" t="n">
-        <v>1420.148131188713</v>
+        <v>1275.981995421499</v>
       </c>
       <c r="U39" t="n">
-        <v>1260.358554911033</v>
+        <v>1116.192419143818</v>
       </c>
       <c r="V39" t="n">
-        <v>1086.105355727679</v>
+        <v>941.9392199604646</v>
       </c>
       <c r="W39" t="n">
-        <v>1086.105355727679</v>
+        <v>941.9392199604646</v>
       </c>
       <c r="X39" t="n">
-        <v>906.4460229545601</v>
+        <v>762.2798871873458</v>
       </c>
       <c r="Y39" t="n">
-        <v>747.464818140283</v>
+        <v>603.2986823730687</v>
       </c>
     </row>
     <row r="40">
@@ -7332,10 +7332,10 @@
         <v>520.6746257234336</v>
       </c>
       <c r="M40" t="n">
-        <v>327.3967344191552</v>
+        <v>520.6746257234336</v>
       </c>
       <c r="N40" t="n">
-        <v>31.68</v>
+        <v>400.1655672929278</v>
       </c>
       <c r="O40" t="n">
         <v>31.68</v>
@@ -7378,25 +7378,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>340.3417231714225</v>
+        <v>662.2374236494027</v>
       </c>
       <c r="C41" t="n">
-        <v>340.3417231714225</v>
+        <v>373.952594599109</v>
       </c>
       <c r="D41" t="n">
-        <v>340.3417231714225</v>
+        <v>373.952594599109</v>
       </c>
       <c r="E41" t="n">
-        <v>340.3417231714225</v>
+        <v>373.952594599109</v>
       </c>
       <c r="F41" t="n">
-        <v>340.3417231714225</v>
+        <v>373.952594599109</v>
       </c>
       <c r="G41" t="n">
-        <v>340.3417231714225</v>
+        <v>64.63267639639733</v>
       </c>
       <c r="H41" t="n">
-        <v>31.68</v>
+        <v>64.63267639639733</v>
       </c>
       <c r="I41" t="n">
         <v>31.68</v>
@@ -7405,22 +7405,22 @@
         <v>423.72</v>
       </c>
       <c r="K41" t="n">
-        <v>490.5460745728644</v>
+        <v>622.7853941879731</v>
       </c>
       <c r="L41" t="n">
-        <v>573.4497292462312</v>
+        <v>705.6890488613399</v>
       </c>
       <c r="M41" t="n">
-        <v>965.4897292462313</v>
+        <v>1097.72904886134</v>
       </c>
       <c r="N41" t="n">
-        <v>965.4897292462313</v>
+        <v>1097.72904886134</v>
       </c>
       <c r="O41" t="n">
-        <v>1357.529729246231</v>
+        <v>1116.69867245535</v>
       </c>
       <c r="P41" t="n">
-        <v>1432.791056790881</v>
+        <v>1191.96</v>
       </c>
       <c r="Q41" t="n">
         <v>1584</v>
@@ -7432,22 +7432,22 @@
         <v>1462.237423649406</v>
       </c>
       <c r="T41" t="n">
-        <v>1062.237423649399</v>
+        <v>1062.237423649404</v>
       </c>
       <c r="U41" t="n">
-        <v>662.2374236493938</v>
+        <v>1062.237423649404</v>
       </c>
       <c r="V41" t="n">
-        <v>662.2374236493938</v>
+        <v>662.2374236494027</v>
       </c>
       <c r="W41" t="n">
-        <v>662.2374236493938</v>
+        <v>662.2374236494027</v>
       </c>
       <c r="X41" t="n">
-        <v>340.3417231714225</v>
+        <v>662.2374236494027</v>
       </c>
       <c r="Y41" t="n">
-        <v>340.3417231714225</v>
+        <v>662.2374236494027</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1101.92327179659</v>
+        <v>1120.621971714599</v>
       </c>
       <c r="C42" t="n">
-        <v>1101.92327179659</v>
+        <v>1120.621971714599</v>
       </c>
       <c r="D42" t="n">
-        <v>1101.92327179659</v>
+        <v>867.1495607068185</v>
       </c>
       <c r="E42" t="n">
-        <v>853.7696382391027</v>
+        <v>618.995927149331</v>
       </c>
       <c r="F42" t="n">
-        <v>608.6825247664998</v>
+        <v>373.9088136767281</v>
       </c>
       <c r="G42" t="n">
-        <v>377.9192809819286</v>
+        <v>143.1455698921569</v>
       </c>
       <c r="H42" t="n">
         <v>143.1455698921569</v>
@@ -7490,10 +7490,10 @@
         <v>749.156560506392</v>
       </c>
       <c r="M42" t="n">
-        <v>905.4900218807156</v>
+        <v>906.4577022492513</v>
       </c>
       <c r="N42" t="n">
-        <v>1111.875903846774</v>
+        <v>1112.84358421531</v>
       </c>
       <c r="O42" t="n">
         <v>1417.795694775776</v>
@@ -7505,28 +7505,28 @@
         <v>1584</v>
       </c>
       <c r="R42" t="n">
-        <v>1584</v>
+        <v>1183.999999999998</v>
       </c>
       <c r="S42" t="n">
-        <v>1584</v>
+        <v>1120.621971714599</v>
       </c>
       <c r="T42" t="n">
-        <v>1584</v>
+        <v>1120.621971714599</v>
       </c>
       <c r="U42" t="n">
-        <v>1277.745777257673</v>
+        <v>1120.621971714599</v>
       </c>
       <c r="V42" t="n">
-        <v>1277.745777257673</v>
+        <v>1120.621971714599</v>
       </c>
       <c r="W42" t="n">
-        <v>1277.745777257673</v>
+        <v>1120.621971714599</v>
       </c>
       <c r="X42" t="n">
-        <v>1277.745777257673</v>
+        <v>1120.621971714599</v>
       </c>
       <c r="Y42" t="n">
-        <v>1277.745777257673</v>
+        <v>1120.621971714599</v>
       </c>
     </row>
     <row r="43">
@@ -7536,16 +7536,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.68</v>
+        <v>54.96405872925319</v>
       </c>
       <c r="C43" t="n">
-        <v>31.68</v>
+        <v>54.96405872925319</v>
       </c>
       <c r="D43" t="n">
-        <v>31.68</v>
+        <v>54.96405872925319</v>
       </c>
       <c r="E43" t="n">
-        <v>31.68</v>
+        <v>54.96405872925319</v>
       </c>
       <c r="F43" t="n">
         <v>31.68</v>
@@ -7590,22 +7590,22 @@
         <v>109.4543695049103</v>
       </c>
       <c r="T43" t="n">
-        <v>31.68</v>
+        <v>109.4543695049103</v>
       </c>
       <c r="U43" t="n">
-        <v>31.68</v>
+        <v>54.96405872925319</v>
       </c>
       <c r="V43" t="n">
-        <v>31.68</v>
+        <v>54.96405872925319</v>
       </c>
       <c r="W43" t="n">
-        <v>31.68</v>
+        <v>54.96405872925319</v>
       </c>
       <c r="X43" t="n">
-        <v>31.68</v>
+        <v>54.96405872925319</v>
       </c>
       <c r="Y43" t="n">
-        <v>31.68</v>
+        <v>54.96405872925319</v>
       </c>
     </row>
     <row r="44">
@@ -7615,40 +7615,40 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1057.228016623573</v>
+        <v>708.5586104979473</v>
       </c>
       <c r="C44" t="n">
-        <v>695.132483044791</v>
+        <v>708.5586104979473</v>
       </c>
       <c r="D44" t="n">
-        <v>372.5676792671649</v>
+        <v>385.9938067203211</v>
       </c>
       <c r="E44" t="n">
-        <v>372.5676792671649</v>
+        <v>385.9938067203211</v>
       </c>
       <c r="F44" t="n">
-        <v>372.5676792671649</v>
+        <v>385.9938067203211</v>
       </c>
       <c r="G44" t="n">
-        <v>372.5676792671649</v>
+        <v>70.61328245700339</v>
       </c>
       <c r="H44" t="n">
-        <v>57.84535003513633</v>
+        <v>70.61328245700339</v>
       </c>
       <c r="I44" t="n">
         <v>31.6</v>
       </c>
       <c r="J44" t="n">
-        <v>422.65</v>
+        <v>41.49557115404399</v>
       </c>
       <c r="K44" t="n">
-        <v>489.4760745728644</v>
+        <v>432.545571154044</v>
       </c>
       <c r="L44" t="n">
-        <v>572.3797292462311</v>
+        <v>515.4492258274108</v>
       </c>
       <c r="M44" t="n">
-        <v>703.6690488613399</v>
+        <v>906.4992258274108</v>
       </c>
       <c r="N44" t="n">
         <v>1094.71904886134</v>
@@ -7663,28 +7663,28 @@
         <v>1580</v>
       </c>
       <c r="R44" t="n">
-        <v>1452.1768175888</v>
+        <v>1580</v>
       </c>
       <c r="S44" t="n">
-        <v>1452.1768175888</v>
+        <v>1184.286963135565</v>
       </c>
       <c r="T44" t="n">
-        <v>1452.1768175888</v>
+        <v>1107.548509487848</v>
       </c>
       <c r="U44" t="n">
-        <v>1452.1768175888</v>
+        <v>1107.548509487848</v>
       </c>
       <c r="V44" t="n">
-        <v>1452.1768175888</v>
+        <v>1107.548509487848</v>
       </c>
       <c r="W44" t="n">
-        <v>1452.1768175888</v>
+        <v>1107.548509487848</v>
       </c>
       <c r="X44" t="n">
-        <v>1452.1768175888</v>
+        <v>1107.548509487848</v>
       </c>
       <c r="Y44" t="n">
-        <v>1452.1768175888</v>
+        <v>708.5586104979473</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>343.2798181307687</v>
+        <v>792.3997637677996</v>
       </c>
       <c r="C45" t="n">
-        <v>149.126175952763</v>
+        <v>519.5715693783862</v>
       </c>
       <c r="D45" t="n">
-        <v>149.126175952763</v>
+        <v>519.5715693783862</v>
       </c>
       <c r="E45" t="n">
-        <v>149.126175952763</v>
+        <v>519.5715693783862</v>
       </c>
       <c r="F45" t="n">
-        <v>149.126175952763</v>
+        <v>268.4238498451772</v>
       </c>
       <c r="G45" t="n">
-        <v>149.126175952763</v>
+        <v>31.6</v>
       </c>
       <c r="H45" t="n">
-        <v>149.126175952763</v>
+        <v>31.6</v>
       </c>
       <c r="I45" t="n">
         <v>31.6</v>
@@ -7724,13 +7724,13 @@
         <v>416.6948404206257</v>
       </c>
       <c r="L45" t="n">
-        <v>744.1888801378564</v>
+        <v>749.0765605063918</v>
       </c>
       <c r="M45" t="n">
-        <v>901.4900218807156</v>
+        <v>906.3777022492511</v>
       </c>
       <c r="N45" t="n">
-        <v>1107.875903846774</v>
+        <v>1112.76358421531</v>
       </c>
       <c r="O45" t="n">
         <v>1413.795694775776</v>
@@ -7748,22 +7748,22 @@
         <v>1580</v>
       </c>
       <c r="T45" t="n">
-        <v>1263.62287866346</v>
+        <v>1580</v>
       </c>
       <c r="U45" t="n">
-        <v>951.3080498605273</v>
+        <v>1400.427995497558</v>
       </c>
       <c r="V45" t="n">
-        <v>951.3080498605273</v>
+        <v>1400.427995497558</v>
       </c>
       <c r="W45" t="n">
-        <v>951.3080498605273</v>
+        <v>1400.427995497558</v>
       </c>
       <c r="X45" t="n">
-        <v>951.3080498605273</v>
+        <v>1400.427995497558</v>
       </c>
       <c r="Y45" t="n">
-        <v>639.8015925209976</v>
+        <v>1088.921538158029</v>
       </c>
     </row>
     <row r="46">
@@ -7773,25 +7773,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="C46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="D46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="E46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="F46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="G46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="H46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="I46" t="n">
         <v>31.6</v>
@@ -7827,22 +7827,22 @@
         <v>103.4343695049103</v>
       </c>
       <c r="T46" t="n">
-        <v>103.4343695049103</v>
+        <v>92.15091683626321</v>
       </c>
       <c r="U46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="V46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="W46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="X46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>103.4343695049103</v>
+        <v>31.6</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>127.519669210766</v>
       </c>
       <c r="K2" t="n">
         <v>631.4989145728644</v>
@@ -7973,16 +7973,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>833.5075211493358</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>382.5631691251116</v>
+        <v>1081.563169125112</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>622.9784570256061</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8207,22 +8207,22 @@
         <v>631.4989145728644</v>
       </c>
       <c r="L5" t="n">
-        <v>615.2589346733669</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>589.9093300807372</v>
+        <v>1081.563169125112</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>610.0289674856534</v>
       </c>
       <c r="Q5" t="n">
-        <v>615.8520732695737</v>
+        <v>129.4282014129126</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,13 +8441,13 @@
         <v>3.914573581773752</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>631.4989145728644</v>
       </c>
       <c r="L8" t="n">
-        <v>151.2867891297963</v>
+        <v>615.2589346733669</v>
       </c>
       <c r="M8" t="n">
-        <v>1060.271045550332</v>
+        <v>587.7784424595038</v>
       </c>
       <c r="N8" t="n">
         <v>382.5631691251116</v>
@@ -8456,7 +8456,7 @@
         <v>679.8387640464542</v>
       </c>
       <c r="P8" t="n">
-        <v>622.9784570256061</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8675,13 +8675,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>631.4989145728644</v>
       </c>
       <c r="L11" t="n">
-        <v>615.258934673367</v>
+        <v>71.31724496834113</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>273.1045615512555</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,16 +8915,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>631.4989145728642</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>615.2589346733669</v>
+        <v>272.5114229550487</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>607.6507146905903</v>
+        <v>1081.563169125112</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>115.5181014129125</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,16 +9152,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>631.4989145728642</v>
+        <v>432.3508340445894</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>781.830661997196</v>
       </c>
       <c r="N17" t="n">
-        <v>382.5631691251116</v>
+        <v>1081.563169125112</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>622.9784570256061</v>
       </c>
       <c r="Q17" t="n">
-        <v>336.9296373315011</v>
+        <v>115.5181014129125</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>89.60073757318966</v>
       </c>
       <c r="L20" t="n">
-        <v>279.9247028481124</v>
+        <v>616.2589346733669</v>
       </c>
       <c r="M20" t="n">
-        <v>451.0840572905585</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>382.5631691251116</v>
+        <v>1082.563169125112</v>
       </c>
       <c r="O20" t="n">
-        <v>680.8387640464542</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>623.9784570256061</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9626,7 +9626,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>628.3659094213435</v>
+        <v>628.3659094214258</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9635,10 +9635,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>729.7521953641688</v>
+        <v>382.5631691251116</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>347.1890262389733</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -9860,16 +9860,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>199.6010868744592</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>123.5795439000653</v>
       </c>
       <c r="M26" t="n">
-        <v>451.0840572905585</v>
+        <v>847.0840572905585</v>
       </c>
       <c r="N26" t="n">
         <v>778.5631691251116</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>319.978457025606</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>511.5181014129125</v>
@@ -9942,7 +9942,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K27" t="n">
-        <v>295.8802408630135</v>
+        <v>294.9027859453008</v>
       </c>
       <c r="L27" t="n">
         <v>388.0893364597981</v>
@@ -9954,7 +9954,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O27" t="n">
-        <v>381.7043438831912</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P27" t="n">
         <v>219.1507118405495</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>123.5795439000654</v>
+        <v>386.0044735817738</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10106,13 +10106,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>847.0840572905585</v>
+        <v>451.0840572905585</v>
       </c>
       <c r="N29" t="n">
-        <v>778.5631691251116</v>
+        <v>535.299475396949</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>376.8387640464542</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K30" t="n">
-        <v>294.902785945301</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L30" t="n">
         <v>388.0893364597981</v>
@@ -10191,7 +10191,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O30" t="n">
-        <v>382.6817988009037</v>
+        <v>381.704343883191</v>
       </c>
       <c r="P30" t="n">
         <v>219.1507118405495</v>
@@ -10337,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>328.4989145728643</v>
+        <v>123.5795439000653</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>306.5987307401135</v>
+        <v>511.5181014129125</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10422,10 +10422,10 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M33" t="n">
-        <v>471.6948204301074</v>
+        <v>470.7173655123947</v>
       </c>
       <c r="N33" t="n">
-        <v>484.4310722536378</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O33" t="n">
         <v>382.6817988009037</v>
@@ -10571,10 +10571,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>386.0044735817738</v>
       </c>
       <c r="K35" t="n">
-        <v>142.7407798536111</v>
+        <v>133.5750703182917</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,16 +10583,16 @@
         <v>847.0840572905585</v>
       </c>
       <c r="N35" t="n">
-        <v>382.5631691251116</v>
+        <v>778.5631691251116</v>
       </c>
       <c r="O35" t="n">
-        <v>376.8387640464542</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>511.5181014129125</v>
+        <v>115.5181014129125</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10662,10 +10662,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>484.4310722536375</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>382.6817988009037</v>
+        <v>381.704343883191</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10808,22 +10808,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>386.0044735817738</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>133.5750703182916</v>
       </c>
       <c r="M38" t="n">
-        <v>847.0840572905585</v>
+        <v>451.0840572905585</v>
       </c>
       <c r="N38" t="n">
         <v>778.5631691251116</v>
       </c>
       <c r="O38" t="n">
-        <v>123.5795439000653</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -10890,10 +10890,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
-        <v>295.8802408630135</v>
+        <v>294.9027859453008</v>
       </c>
       <c r="L39" t="n">
-        <v>387.1118815420854</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -11048,7 +11048,7 @@
         <v>386.0044735817738</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>133.5750703182917</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11060,13 +11060,13 @@
         <v>382.5631691251116</v>
       </c>
       <c r="O41" t="n">
-        <v>376.8387640464542</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>268.2544076847498</v>
+        <v>511.5181014129125</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11133,13 +11133,13 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M42" t="n">
-        <v>470.7173655123947</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>382.6817988009037</v>
+        <v>381.704343883191</v>
       </c>
       <c r="P42" t="n">
         <v>219.1507118405495</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>385.0044735817738</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>327.4989145728644</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>583.6995316492541</v>
+        <v>846.0840572905585</v>
       </c>
       <c r="N44" t="n">
-        <v>777.5631691251116</v>
+        <v>572.6842024927167</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11367,7 +11367,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>383.1522855824895</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -11376,7 +11376,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>382.6817988009037</v>
+        <v>377.7447479235951</v>
       </c>
       <c r="P45" t="n">
         <v>219.1507118405495</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>83.31889009107448</v>
       </c>
       <c r="N4" t="n">
         <v>134.7595670749636</v>
@@ -22715,10 +22715,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>114.2072877307173</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>30.88839763964455</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>83.31889009107448</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>56.54936802558444</v>
+        <v>139.8682581166618</v>
       </c>
       <c r="R7" t="n">
         <v>315.8993083090199</v>
@@ -23177,22 +23177,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>83.31889009107448</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>113.7897626128787</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>258.6589137217201</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>139.8682581166501</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>315.8993083090199</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23223,13 +23223,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>166.9762276721997</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>237.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>198.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>192.3632896068686</v>
@@ -23238,7 +23238,7 @@
         <v>192.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>191.2267190206846</v>
       </c>
       <c r="H11" t="n">
         <v>190.5751059397083</v>
@@ -23283,13 +23283,13 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>417.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>376.1656565089042</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -23411,10 +23411,10 @@
         <v>48.86569183392993</v>
       </c>
       <c r="L13" t="n">
-        <v>169.7715045767194</v>
+        <v>176.1586445512218</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>271.3188900910745</v>
       </c>
       <c r="N13" t="n">
         <v>322.7595670749636</v>
@@ -23429,7 +23429,7 @@
         <v>493.907266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>503.8993083090199</v>
+        <v>226.193278243443</v>
       </c>
       <c r="S13" t="n">
         <v>146.2252174077735</v>
@@ -23466,19 +23466,19 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>192.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>186.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>186.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>185.2267190206845</v>
+        <v>185.2267190206846</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>184.5751059397083</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,13 +23511,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>264.7559064957902</v>
+        <v>112.9664380403345</v>
       </c>
       <c r="T14" t="n">
-        <v>264.7250547720239</v>
+        <v>366.3526470551971</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>431.1788442873041</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>69.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>54.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>67.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>62.98090483695654</v>
@@ -23666,10 +23666,10 @@
         <v>487.907266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>178.7902782434431</v>
+        <v>497.8993083090199</v>
       </c>
       <c r="S16" t="n">
-        <v>140.2252174077735</v>
+        <v>111.4004506624454</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23684,10 +23684,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>29.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>69.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -23715,7 +23715,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>6.299754343229012</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.29975434322904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -23885,28 +23885,28 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>79.15864455122178</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>174.3188900910745</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>225.7595670749636</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>174.5738174589902</v>
       </c>
       <c r="P19" t="n">
-        <v>349.6589137217201</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>353.3772228623035</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>49.22521740777347</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.418954343228961</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23991,7 +23991,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.418954343229018</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>79.15864455122178</v>
+        <v>79.15864455122181</v>
       </c>
       <c r="M22" t="n">
         <v>174.3188900910745</v>
@@ -24131,13 +24131,13 @@
         <v>225.7595670749636</v>
       </c>
       <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>174.5738174589902</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.418954343228961</v>
+        <v>2.418954343229103</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>79.15864455122181</v>
+        <v>79.15864455122178</v>
       </c>
       <c r="M25" t="n">
         <v>174.3188900910745</v>
@@ -24411,13 +24411,13 @@
         <v>239.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>207.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>168.3391557398498</v>
+        <v>14.38131576321453</v>
       </c>
       <c r="E26" t="n">
-        <v>162.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>162.8896287080119</v>
@@ -24426,7 +24426,7 @@
         <v>161.2267190206846</v>
       </c>
       <c r="H26" t="n">
-        <v>160.5751059397083</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,22 +24459,22 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>240.7559064957902</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>342.3526470551971</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>11.17884428730144</v>
+        <v>407.1788442873041</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>387.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3734759809451589</v>
+        <v>396.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>262.6534903103031</v>
+        <v>350.2818334606677</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24499,7 +24499,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>97.63624233787687</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -24535,7 +24535,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>287.645570877285</v>
+        <v>188.3248656614027</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -24544,10 +24544,10 @@
         <v>162.2133501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>158.1916805149037</v>
       </c>
       <c r="V27" t="n">
-        <v>156.5072176368983</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -24566,19 +24566,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>30.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>43.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>38.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>32.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>2.805840054644786</v>
@@ -24608,16 +24608,16 @@
         <v>364.8007116199985</v>
       </c>
       <c r="P28" t="n">
-        <v>328.5542342555209</v>
+        <v>416.6589137217201</v>
       </c>
       <c r="Q28" t="n">
-        <v>67.907266425598</v>
+        <v>463.907266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>473.8993083090199</v>
+        <v>342.2242249454339</v>
       </c>
       <c r="S28" t="n">
-        <v>116.2252174077735</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24635,7 +24635,7 @@
         <v>5.443645430107551</v>
       </c>
       <c r="Y28" t="n">
-        <v>45.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -24645,22 +24645,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>239.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>69.18023080910457</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>162.3632896068686</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>161.2267190206845</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24699,10 +24699,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>254.9069678199323</v>
       </c>
       <c r="U29" t="n">
-        <v>407.1788442873041</v>
+        <v>407.1788442873042</v>
       </c>
       <c r="V29" t="n">
         <v>387.8510241668239</v>
@@ -24714,7 +24714,7 @@
         <v>350.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>269.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24724,10 +24724,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>142.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>119.0999124455193</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -24772,25 +24772,25 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>113.4504408077594</v>
       </c>
       <c r="S30" t="n">
-        <v>219.2902263797056</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>162.2133501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>158.1916805149037</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>172.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>185.756528611457</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>177.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -24818,7 +24818,7 @@
         <v>32.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>2.805840054644786</v>
+        <v>2.80584005464479</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -24839,10 +24839,10 @@
         <v>241.3188900910745</v>
       </c>
       <c r="N31" t="n">
-        <v>292.7595670749636</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>364.8007116199985</v>
+        <v>173.4555992287629</v>
       </c>
       <c r="P31" t="n">
         <v>416.6589137217201</v>
@@ -24851,10 +24851,10 @@
         <v>463.907266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>77.89930830901991</v>
+        <v>473.8993083090199</v>
       </c>
       <c r="S31" t="n">
-        <v>28.12053794157426</v>
+        <v>116.2252174077735</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24882,16 +24882,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>239.9993129555745</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>207.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>168.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>162.3632896068686</v>
       </c>
       <c r="F32" t="n">
         <v>162.8896287080119</v>
@@ -24939,16 +24939,16 @@
         <v>342.3526470551971</v>
       </c>
       <c r="U32" t="n">
-        <v>407.1788442873041</v>
+        <v>11.17884428730213</v>
       </c>
       <c r="V32" t="n">
-        <v>387.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>257.3522786697087</v>
+        <v>0.37347598094766</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>262.6534903103</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -24967,16 +24967,16 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>105.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>100.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>97.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>83.45561134672546</v>
       </c>
       <c r="H33" t="n">
         <v>87.42597397887397</v>
@@ -25009,10 +25009,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>114.5038242668049</v>
+        <v>287.645570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>219.2902263797056</v>
+        <v>76.5657519701638</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -25024,7 +25024,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>190.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -25040,16 +25040,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>45.11380033707866</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>30.72524664804467</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>43.53621805555548</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>38.98090483695654</v>
       </c>
       <c r="F34" t="n">
         <v>32.38285596774193</v>
@@ -25085,13 +25085,13 @@
         <v>416.6589137217201</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.907266425598</v>
+        <v>375.8025869593988</v>
       </c>
       <c r="R34" t="n">
-        <v>309.8413689776919</v>
+        <v>77.89930830901991</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>116.2252174077735</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25109,7 +25109,7 @@
         <v>5.443645430107551</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>45.46535284946236</v>
       </c>
     </row>
     <row r="35">
@@ -25137,7 +25137,7 @@
         <v>161.2267190206846</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>160.5751059397083</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25170,25 +25170,25 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>240.7559064957902</v>
       </c>
       <c r="T35" t="n">
-        <v>342.3526470551971</v>
+        <v>209.0061373654949</v>
       </c>
       <c r="U35" t="n">
-        <v>17.99489018347299</v>
+        <v>407.1788442873041</v>
       </c>
       <c r="V35" t="n">
-        <v>387.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.3734759809451589</v>
+        <v>0.37347598094766</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>269.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -25198,19 +25198,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>142.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>119.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>105.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>100.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>97.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>83.45561134672546</v>
@@ -25246,10 +25246,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>287.645570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>163.9917259490374</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -25261,7 +25261,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>76.10794418681341</v>
+        <v>190.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -25310,13 +25310,13 @@
         <v>146.1586445512218</v>
       </c>
       <c r="M37" t="n">
-        <v>241.3188900910745</v>
+        <v>49.97377769983888</v>
       </c>
       <c r="N37" t="n">
-        <v>173.4555992287629</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>364.8007116199985</v>
       </c>
       <c r="P37" t="n">
         <v>416.6589137217201</v>
@@ -25356,25 +25356,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>239.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>207.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>168.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>162.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>162.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>161.2267190206846</v>
+        <v>122.0709902136938</v>
       </c>
       <c r="H38" t="n">
-        <v>160.5751059397083</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25410,22 +25410,22 @@
         <v>240.7559064957902</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>342.3526470551971</v>
       </c>
       <c r="U38" t="n">
-        <v>265.903148192133</v>
+        <v>11.17884428730213</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>387.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>0.3734759809460684</v>
+        <v>396.3734759809475</v>
       </c>
       <c r="X38" t="n">
         <v>350.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>269.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>83.45561134672546</v>
       </c>
       <c r="H39" t="n">
-        <v>28.1571109160574</v>
+        <v>87.42597397887397</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -25483,7 +25483,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>287.645570877285</v>
+        <v>144.9210964677431</v>
       </c>
       <c r="S39" t="n">
         <v>219.2902263797056</v>
@@ -25547,13 +25547,13 @@
         <v>146.1586445512218</v>
       </c>
       <c r="M40" t="n">
-        <v>49.97377769983888</v>
+        <v>241.3188900910745</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>173.4555992287629</v>
       </c>
       <c r="O40" t="n">
-        <v>364.8007116199985</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>416.6589137217201</v>
@@ -25596,7 +25596,7 @@
         <v>384.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>352.4745782429939</v>
+        <v>67.0725974832032</v>
       </c>
       <c r="D41" t="n">
         <v>313.3391557398498</v>
@@ -25608,13 +25608,13 @@
         <v>307.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>306.2267190206845</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>305.5751059397083</v>
       </c>
       <c r="I41" t="n">
-        <v>32.62314963243335</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25647,19 +25647,19 @@
         <v>385.7559064957902</v>
       </c>
       <c r="T41" t="n">
-        <v>91.3526470551908</v>
+        <v>91.3526470551958</v>
       </c>
       <c r="U41" t="n">
-        <v>156.1788442872987</v>
+        <v>552.1788442873042</v>
       </c>
       <c r="V41" t="n">
-        <v>532.8510241668239</v>
+        <v>136.8510241668223</v>
       </c>
       <c r="W41" t="n">
         <v>541.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>176.6050899874762</v>
+        <v>495.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>414.3174326828064</v>
@@ -25672,13 +25672,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>113.4922762398547</v>
+        <v>287.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>264.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>250.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -25690,7 +25690,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>232.425973978874</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25720,16 +25720,16 @@
         <v>39.83654810934751</v>
       </c>
       <c r="R42" t="n">
-        <v>432.645570877285</v>
+        <v>36.64557087728349</v>
       </c>
       <c r="S42" t="n">
-        <v>364.2902263797056</v>
+        <v>301.5459783771603</v>
       </c>
       <c r="T42" t="n">
         <v>307.2133501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>303.1916805149037</v>
       </c>
       <c r="V42" t="n">
         <v>317.5106671915202</v>
@@ -25763,7 +25763,7 @@
         <v>183.9809048369565</v>
       </c>
       <c r="F43" t="n">
-        <v>177.3828559677419</v>
+        <v>154.3316378257813</v>
       </c>
       <c r="G43" t="n">
         <v>147.8058400546448</v>
@@ -25805,10 +25805,10 @@
         <v>261.2252174077735</v>
       </c>
       <c r="T43" t="n">
-        <v>35.01089151606865</v>
+        <v>112.0075173259299</v>
       </c>
       <c r="U43" t="n">
-        <v>53.94540766790055</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>102.1703102162162</v>
@@ -25830,10 +25830,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>390.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>358.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -25845,13 +25845,13 @@
         <v>313.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>312.2267190206845</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>311.5751059397083</v>
       </c>
       <c r="I44" t="n">
-        <v>12.64025309764838</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25878,13 +25878,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>126.5449505870884</v>
       </c>
       <c r="S44" t="n">
-        <v>391.7559064957902</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>493.3526470551971</v>
+        <v>417.3815779439567</v>
       </c>
       <c r="U44" t="n">
         <v>558.1788442873042</v>
@@ -25899,7 +25899,7 @@
         <v>501.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>420.3174326828064</v>
+        <v>25.31743268280474</v>
       </c>
     </row>
     <row r="45">
@@ -25912,7 +25912,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>77.88780668929365</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>256.9376868977026</v>
@@ -25921,16 +25921,16 @@
         <v>251.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>248.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>234.4556113467254</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>238.425973978874</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>116.3509141932353</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25963,10 +25963,10 @@
         <v>370.2902263797056</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>313.2133501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>131.4153960574863</v>
       </c>
       <c r="V45" t="n">
         <v>323.5106671915202</v>
@@ -26009,7 +26009,7 @@
         <v>135.6547982327662</v>
       </c>
       <c r="I46" t="n">
-        <v>7.359134728289821</v>
+        <v>78.47516053815106</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -26042,10 +26042,10 @@
         <v>267.2252174077735</v>
       </c>
       <c r="T46" t="n">
-        <v>118.0075173259298</v>
+        <v>106.8368991839692</v>
       </c>
       <c r="U46" t="n">
-        <v>59.94540766790056</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>108.1703102162162</v>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2739570.010586282</v>
+        <v>2739570.010586283</v>
       </c>
     </row>
     <row r="5">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4199855.543090831</v>
+        <v>4199855.543090832</v>
       </c>
     </row>
     <row r="7">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7345778.187010864</v>
+        <v>7345778.187010868</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8023999.380689378</v>
+        <v>8023999.380689379</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8702220.574367896</v>
+        <v>8702220.574367894</v>
       </c>
     </row>
     <row r="13">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10923954.88627446</v>
+        <v>10923954.88627445</v>
       </c>
     </row>
   </sheetData>
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1342071.515143757</v>
+        <v>1342071.515143758</v>
       </c>
       <c r="C2" t="n">
-        <v>1342071.515143757</v>
+        <v>1342071.515143758</v>
       </c>
       <c r="D2" t="n">
-        <v>1342071.515143757</v>
+        <v>1342071.515143758</v>
       </c>
       <c r="E2" t="n">
         <v>1158920.0821918</v>
@@ -26284,34 +26284,34 @@
         <v>1170282.241013537</v>
       </c>
       <c r="G2" t="n">
-        <v>1335152.916054522</v>
+        <v>1335152.916054521</v>
       </c>
       <c r="H2" t="n">
+        <v>1335484.99611052</v>
+      </c>
+      <c r="I2" t="n">
         <v>1335484.996110522</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1335484.996110521</v>
       </c>
       <c r="J2" t="n">
         <v>1080130.049191716</v>
       </c>
       <c r="K2" t="n">
-        <v>1080130.049191716</v>
+        <v>1080130.049191715</v>
       </c>
       <c r="L2" t="n">
         <v>1080130.049191716</v>
       </c>
       <c r="M2" t="n">
+        <v>1080130.049191715</v>
+      </c>
+      <c r="N2" t="n">
         <v>1080130.049191716</v>
       </c>
-      <c r="N2" t="n">
-        <v>1080130.049191715</v>
-      </c>
       <c r="O2" t="n">
-        <v>697763.5716412984</v>
+        <v>697763.571641298</v>
       </c>
       <c r="P2" t="n">
-        <v>680678.6052412988</v>
+        <v>680678.6052412989</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>644047.1874876738</v>
+        <v>648034.5426922527</v>
       </c>
       <c r="C4" t="n">
-        <v>642311.349263161</v>
+        <v>646298.7044677399</v>
       </c>
       <c r="D4" t="n">
-        <v>640573.1562657534</v>
+        <v>644560.5114703323</v>
       </c>
       <c r="E4" t="n">
-        <v>540312.0173187121</v>
+        <v>544257.1980145414</v>
       </c>
       <c r="F4" t="n">
-        <v>544878.3098753577</v>
+        <v>548823.4905711869</v>
       </c>
       <c r="G4" t="n">
-        <v>629484.9374769011</v>
+        <v>633433.1524397441</v>
       </c>
       <c r="H4" t="n">
-        <v>627728.281360092</v>
+        <v>631676.496322935</v>
       </c>
       <c r="I4" t="n">
-        <v>625992.4902287903</v>
+        <v>629940.7051916332</v>
       </c>
       <c r="J4" t="n">
-        <v>496555.1079179476</v>
+        <v>499599.5953536326</v>
       </c>
       <c r="K4" t="n">
-        <v>495148.9396798648</v>
+        <v>498193.4271155498</v>
       </c>
       <c r="L4" t="n">
-        <v>493740.7735443832</v>
+        <v>496785.2609800682</v>
       </c>
       <c r="M4" t="n">
-        <v>492330.5947578949</v>
+        <v>495375.08219358</v>
       </c>
       <c r="N4" t="n">
-        <v>490918.3883688038</v>
+        <v>493962.8758044888</v>
       </c>
       <c r="O4" t="n">
-        <v>296309.3215634229</v>
+        <v>299353.8089991079</v>
       </c>
       <c r="P4" t="n">
-        <v>287149.2089231687</v>
+        <v>290189.1423631235</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>244271.9276560836</v>
+        <v>240284.5724515053</v>
       </c>
       <c r="C6" t="n">
-        <v>620755.7658805965</v>
+        <v>616768.4106760178</v>
       </c>
       <c r="D6" t="n">
-        <v>622493.958878004</v>
+        <v>618506.6036734259</v>
       </c>
       <c r="E6" t="n">
-        <v>385808.6368730874</v>
+        <v>381863.4561772586</v>
       </c>
       <c r="F6" t="n">
-        <v>556900.0891381791</v>
+        <v>552954.9084423506</v>
       </c>
       <c r="G6" t="n">
-        <v>561513.8575776208</v>
+        <v>557565.6426147771</v>
       </c>
       <c r="H6" t="n">
-        <v>635989.79375043</v>
+        <v>632041.5787875854</v>
       </c>
       <c r="I6" t="n">
-        <v>638077.5848817305</v>
+        <v>634129.3699188888</v>
       </c>
       <c r="J6" t="n">
-        <v>281235.8432737683</v>
+        <v>278191.3558380835</v>
       </c>
       <c r="K6" t="n">
-        <v>532882.0115118516</v>
+        <v>529837.5240761654</v>
       </c>
       <c r="L6" t="n">
-        <v>466290.1776473324</v>
+        <v>463245.6902116477</v>
       </c>
       <c r="M6" t="n">
-        <v>540500.3564338209</v>
+        <v>537455.8689981354</v>
       </c>
       <c r="N6" t="n">
-        <v>541912.5628229117</v>
+        <v>538868.0753872276</v>
       </c>
       <c r="O6" t="n">
-        <v>366345.1570778755</v>
+        <v>363300.6696421902</v>
       </c>
       <c r="P6" t="n">
-        <v>358985.5173181301</v>
+        <v>355945.5838781754</v>
       </c>
     </row>
   </sheetData>
@@ -27442,19 +27442,19 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>279.4678545627506</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>129.6231496324334</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>217.5449505870885</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>332.2997543432287</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.4556113467254</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>329.425973978874</v>
       </c>
       <c r="I3" t="n">
-        <v>207.3509141932353</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,7 +27560,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>22.26903443182141</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27572,13 +27572,13 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>178.5322041725895</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>169.475160538151</v>
       </c>
       <c r="J4" t="n">
-        <v>237.1985049982195</v>
+        <v>369.1922490199365</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>260.8656918339299</v>
       </c>
       <c r="L4" t="n">
         <v>388.1586445512218</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>358.2252174077735</v>
       </c>
       <c r="T4" t="n">
         <v>209.0075173259299</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9454076679006</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27657,10 +27657,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27679,19 +27679,19 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>149.8447049303173</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>129.6231496324334</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27724,7 +27724,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>279.4678545627503</v>
+        <v>400</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27749,16 +27749,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27770,7 +27770,7 @@
         <v>329.425973978874</v>
       </c>
       <c r="I6" t="n">
-        <v>207.3509141932353</v>
+        <v>131.0748808363242</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27815,10 +27815,10 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>212.6611401907131</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -27828,34 +27828,34 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C7" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D7" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E7" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F7" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G7" t="n">
         <v>400</v>
       </c>
-      <c r="C7" t="n">
+      <c r="H7" t="n">
+        <v>226.6547982327662</v>
+      </c>
+      <c r="I7" t="n">
         <v>400</v>
       </c>
-      <c r="D7" t="n">
+      <c r="J7" t="n">
         <v>400</v>
       </c>
-      <c r="E7" t="n">
-        <v>400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>400</v>
-      </c>
-      <c r="G7" t="n">
-        <v>244.8058400546448</v>
-      </c>
-      <c r="H7" t="n">
-        <v>249.6121504263232</v>
-      </c>
-      <c r="I7" t="n">
-        <v>169.475160538151</v>
-      </c>
-      <c r="J7" t="n">
-        <v>18.44003080312089</v>
-      </c>
       <c r="K7" t="n">
-        <v>260.8656918339299</v>
+        <v>306.7975322520936</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,7 +27882,7 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>209.0075173259299</v>
       </c>
       <c r="U7" t="n">
         <v>150.9454076679006</v>
@@ -27910,7 +27910,7 @@
         <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -27922,46 +27922,46 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
+        <v>279.4678545627506</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>400</v>
-      </c>
-      <c r="H8" t="n">
-        <v>400</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>217.5449505870885</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>61.92290397566182</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27986,22 +27986,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>139.1351569807732</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.4556113467254</v>
       </c>
       <c r="H9" t="n">
         <v>329.425973978874</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>136.8365481093475</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>295.0537254423838</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28083,19 +28083,19 @@
         <v>244.8058400546448</v>
       </c>
       <c r="H10" t="n">
-        <v>226.6547982327662</v>
+        <v>278.5630985144534</v>
       </c>
       <c r="I10" t="n">
-        <v>169.475160538151</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>18.44003080312089</v>
+        <v>400</v>
       </c>
       <c r="K10" t="n">
         <v>260.8656918339299</v>
       </c>
       <c r="L10" t="n">
-        <v>388.1586445512218</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28119,22 +28119,22 @@
         <v>358.2252174077735</v>
       </c>
       <c r="T10" t="n">
-        <v>209.0075173259299</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9454076679006</v>
       </c>
       <c r="V10" t="n">
-        <v>378.2244730656567</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28244,16 +28244,16 @@
         <v>212</v>
       </c>
       <c r="I12" t="n">
-        <v>207.3509141932353</v>
+        <v>212</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="K12" t="n">
-        <v>63.19186646260397</v>
+        <v>212</v>
       </c>
       <c r="L12" t="n">
-        <v>212</v>
+        <v>58.54278065583941</v>
       </c>
       <c r="M12" t="n">
         <v>212</v>
@@ -28262,7 +28262,7 @@
         <v>212</v>
       </c>
       <c r="O12" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>212</v>
@@ -28490,13 +28490,13 @@
         <v>218</v>
       </c>
       <c r="L15" t="n">
-        <v>142.7154161012017</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="N15" t="n">
-        <v>218</v>
+        <v>142.7154161012016</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.50804751802593</v>
+        <v>309</v>
       </c>
       <c r="C18" t="n">
         <v>309</v>
@@ -28709,7 +28709,7 @@
         <v>309</v>
       </c>
       <c r="F18" t="n">
-        <v>309</v>
+        <v>165.3445956273741</v>
       </c>
       <c r="G18" t="n">
         <v>309</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>136.8365481093475</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>309</v>
@@ -28937,7 +28937,7 @@
         <v>309</v>
       </c>
       <c r="C21" t="n">
-        <v>309</v>
+        <v>28.50804751802599</v>
       </c>
       <c r="D21" t="n">
         <v>309</v>
@@ -28985,7 +28985,7 @@
         <v>309</v>
       </c>
       <c r="S21" t="n">
-        <v>28.50804751802633</v>
+        <v>309</v>
       </c>
       <c r="T21" t="n">
         <v>309</v>
@@ -29189,7 +29189,7 @@
         <v>309</v>
       </c>
       <c r="H24" t="n">
-        <v>28.50804751802605</v>
+        <v>309</v>
       </c>
       <c r="I24" t="n">
         <v>207.3509141932353</v>
@@ -29228,7 +29228,7 @@
         <v>309</v>
       </c>
       <c r="U24" t="n">
-        <v>309</v>
+        <v>28.5080475180261</v>
       </c>
       <c r="V24" t="n">
         <v>309</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
@@ -34901,10 +34901,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>218.7584741950986</v>
+        <v>350.7522182168155</v>
       </c>
       <c r="K4" t="n">
-        <v>139.1343081660701</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>41.77478259222653</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0545923320994</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34943,10 +34943,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -35114,34 +35114,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.1941599453552</v>
       </c>
       <c r="H7" t="n">
-        <v>22.95735219355697</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>230.524839461849</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>381.5599691968791</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>45.93184041816369</v>
       </c>
       <c r="L7" t="n">
         <v>11.84135544877819</v>
@@ -35168,7 +35168,7 @@
         <v>41.77478259222653</v>
       </c>
       <c r="T7" t="n">
-        <v>190.9924826740701</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35369,19 +35369,19 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>51.90830028168727</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>230.524839461849</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>381.5599691968791</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>11.84135544877821</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35405,22 +35405,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.9924826740701</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0545923320994</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>179.0541628494405</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,13 +35454,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>440.3002630043829</v>
+        <v>9.995526418226255</v>
       </c>
       <c r="K11" t="n">
-        <v>67.50108542713571</v>
+        <v>699</v>
       </c>
       <c r="L11" t="n">
-        <v>699.0000000000001</v>
+        <v>155.0583102949743</v>
       </c>
       <c r="M11" t="n">
         <v>609.1869882597739</v>
@@ -35475,7 +35475,7 @@
         <v>76.02154297439397</v>
       </c>
       <c r="Q11" t="n">
-        <v>157.5864601383429</v>
+        <v>500.3339718566612</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,16 +35530,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4.649085806764676</v>
       </c>
       <c r="J12" t="n">
-        <v>152.0332477471097</v>
+        <v>364.0332477471097</v>
       </c>
       <c r="K12" t="n">
-        <v>300.1433060090557</v>
+        <v>448.9514395464517</v>
       </c>
       <c r="L12" t="n">
-        <v>547.7391111977436</v>
+        <v>394.281891853583</v>
       </c>
       <c r="M12" t="n">
         <v>370.8900421645043</v>
@@ -35548,7 +35548,7 @@
         <v>420.4705878445039</v>
       </c>
       <c r="O12" t="n">
-        <v>521.0098898272747</v>
+        <v>309.0098898272747</v>
       </c>
       <c r="P12" t="n">
         <v>379.8831365901249</v>
@@ -35694,16 +35694,16 @@
         <v>440.3002630043829</v>
       </c>
       <c r="K14" t="n">
-        <v>699</v>
+        <v>67.50108542713571</v>
       </c>
       <c r="L14" t="n">
-        <v>699</v>
+        <v>356.2524882816818</v>
       </c>
       <c r="M14" t="n">
         <v>609.1869882597739</v>
       </c>
       <c r="N14" t="n">
-        <v>225.0875455654787</v>
+        <v>699</v>
       </c>
       <c r="O14" t="n">
         <v>19.16123595354574</v>
@@ -35712,7 +35712,7 @@
         <v>76.02154297439397</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>500.3339718566612</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,7 +35767,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>10.64908580676469</v>
+        <v>10.64908580676468</v>
       </c>
       <c r="J15" t="n">
         <v>370.0332477471097</v>
@@ -35776,13 +35776,13 @@
         <v>454.9514395464517</v>
       </c>
       <c r="L15" t="n">
-        <v>478.4545272989453</v>
+        <v>335.7391111977436</v>
       </c>
       <c r="M15" t="n">
-        <v>158.8900421645043</v>
+        <v>376.8900421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>426.4705878445039</v>
+        <v>351.1860039457055</v>
       </c>
       <c r="O15" t="n">
         <v>309.0098898272747</v>
@@ -35846,7 +35846,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>48.52483946184896</v>
+        <v>48.52483946184894</v>
       </c>
       <c r="J16" t="n">
         <v>199.5599691968791</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>8.992482674070146</v>
+        <v>8.992482674070155</v>
       </c>
       <c r="U16" t="n">
         <v>67.05459233209945</v>
@@ -35934,13 +35934,13 @@
         <v>699</v>
       </c>
       <c r="L17" t="n">
-        <v>282.8891458548685</v>
+        <v>83.74106532663313</v>
       </c>
       <c r="M17" t="n">
-        <v>609.1869882597739</v>
+        <v>330.7466047066375</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="O17" t="n">
         <v>19.16123595354574</v>
@@ -35949,7 +35949,7 @@
         <v>699</v>
       </c>
       <c r="Q17" t="n">
-        <v>221.4115359185885</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>440.3002630043829</v>
+        <v>9.995526418226255</v>
       </c>
       <c r="K20" t="n">
-        <v>67.50108542713565</v>
+        <v>161.2348281518109</v>
       </c>
       <c r="L20" t="n">
-        <v>367.7987733261569</v>
+        <v>700</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>609.1869882597739</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="O20" t="n">
-        <v>700</v>
+        <v>19.16123595354574</v>
       </c>
       <c r="P20" t="n">
-        <v>700</v>
+        <v>76.02154297439397</v>
       </c>
       <c r="Q20" t="n">
         <v>500.3339718566612</v>
@@ -36320,7 +36320,7 @@
         <v>82.34520176723385</v>
       </c>
       <c r="I22" t="n">
-        <v>139.5248394618489</v>
+        <v>139.524839461849</v>
       </c>
       <c r="J22" t="n">
         <v>290.5599691968791</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>99.99248267407016</v>
+        <v>99.99248267407015</v>
       </c>
       <c r="U22" t="n">
         <v>158.0545923320994</v>
@@ -36414,10 +36414,10 @@
         <v>609.1869882597739</v>
       </c>
       <c r="N23" t="n">
-        <v>347.1890262390572</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>19.16123595354574</v>
+        <v>366.350262192519</v>
       </c>
       <c r="P23" t="n">
         <v>76.02154297439397</v>
@@ -36557,7 +36557,7 @@
         <v>82.34520176723385</v>
       </c>
       <c r="I25" t="n">
-        <v>139.524839461849</v>
+        <v>139.5248394618489</v>
       </c>
       <c r="J25" t="n">
         <v>290.5599691968791</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>99.99248267407015</v>
+        <v>99.99248267407016</v>
       </c>
       <c r="U25" t="n">
         <v>158.0545923320994</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>209.5966132926855</v>
+        <v>9.995526418226255</v>
       </c>
       <c r="K26" t="n">
         <v>67.50108542713568</v>
       </c>
       <c r="L26" t="n">
-        <v>83.74106532663319</v>
+        <v>207.3206092266985</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="N26" t="n">
         <v>396</v>
@@ -36657,7 +36657,7 @@
         <v>19.16123595354574</v>
       </c>
       <c r="P26" t="n">
-        <v>396</v>
+        <v>76.02154297439397</v>
       </c>
       <c r="Q26" t="n">
         <v>396</v>
@@ -36721,7 +36721,7 @@
         <v>152.0332477471097</v>
       </c>
       <c r="K27" t="n">
-        <v>236.9514395464517</v>
+        <v>235.973984628739</v>
       </c>
       <c r="L27" t="n">
         <v>335.7391111977436</v>
@@ -36733,7 +36733,7 @@
         <v>208.4705878445039</v>
       </c>
       <c r="O27" t="n">
-        <v>308.0324349095621</v>
+        <v>309.0098898272747</v>
       </c>
       <c r="P27" t="n">
         <v>167.8831365901249</v>
@@ -36876,22 +36876,22 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>133.5750703182916</v>
+        <v>396</v>
       </c>
       <c r="K29" t="n">
-        <v>67.50108542713568</v>
+        <v>67.50108542713571</v>
       </c>
       <c r="L29" t="n">
-        <v>83.74106532663319</v>
+        <v>83.74106532663313</v>
       </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>152.7363062718373</v>
+      </c>
+      <c r="O29" t="n">
         <v>396</v>
-      </c>
-      <c r="N29" t="n">
-        <v>396</v>
-      </c>
-      <c r="O29" t="n">
-        <v>19.16123595354574</v>
       </c>
       <c r="P29" t="n">
         <v>76.02154297439397</v>
@@ -36958,7 +36958,7 @@
         <v>152.0332477471097</v>
       </c>
       <c r="K30" t="n">
-        <v>235.9739846287392</v>
+        <v>236.9514395464517</v>
       </c>
       <c r="L30" t="n">
         <v>335.7391111977436</v>
@@ -36970,7 +36970,7 @@
         <v>208.4705878445039</v>
       </c>
       <c r="O30" t="n">
-        <v>309.0098898272747</v>
+        <v>308.0324349095619</v>
       </c>
       <c r="P30" t="n">
         <v>167.8831365901249</v>
@@ -37028,10 +37028,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>15.34520176723384</v>
+        <v>15.34520176723385</v>
       </c>
       <c r="I31" t="n">
-        <v>72.52483946184894</v>
+        <v>72.52483946184896</v>
       </c>
       <c r="J31" t="n">
         <v>223.5599691968791</v>
@@ -37116,7 +37116,7 @@
         <v>9.995526418226255</v>
       </c>
       <c r="K32" t="n">
-        <v>396</v>
+        <v>191.080629327201</v>
       </c>
       <c r="L32" t="n">
         <v>83.74106532663319</v>
@@ -37134,7 +37134,7 @@
         <v>76.02154297439397</v>
       </c>
       <c r="Q32" t="n">
-        <v>191.0806293272009</v>
+        <v>396</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37201,10 +37201,10 @@
         <v>335.7391111977436</v>
       </c>
       <c r="M33" t="n">
-        <v>158.8900421645043</v>
+        <v>157.9125872467916</v>
       </c>
       <c r="N33" t="n">
-        <v>207.4931329267913</v>
+        <v>208.4705878445039</v>
       </c>
       <c r="O33" t="n">
         <v>309.0098898272747</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>9.995526418226255</v>
+        <v>396</v>
       </c>
       <c r="K35" t="n">
-        <v>210.2418652807467</v>
+        <v>201.0761557454273</v>
       </c>
       <c r="L35" t="n">
-        <v>83.74106532663319</v>
+        <v>83.74106532663313</v>
       </c>
       <c r="M35" t="n">
         <v>396</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="O35" t="n">
-        <v>396</v>
+        <v>19.16123595354574</v>
       </c>
       <c r="P35" t="n">
         <v>76.02154297439397</v>
       </c>
       <c r="Q35" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37441,10 +37441,10 @@
         <v>158.8900421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>207.4931329267911</v>
+        <v>208.4705878445039</v>
       </c>
       <c r="O36" t="n">
-        <v>309.0098898272747</v>
+        <v>308.0324349095619</v>
       </c>
       <c r="P36" t="n">
         <v>167.8831365901249</v>
@@ -37587,22 +37587,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>9.995526418226255</v>
+        <v>396</v>
       </c>
       <c r="K38" t="n">
-        <v>67.50108542713568</v>
+        <v>67.50108542713571</v>
       </c>
       <c r="L38" t="n">
-        <v>83.74106532663319</v>
+        <v>217.3161356449248</v>
       </c>
       <c r="M38" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>396</v>
       </c>
       <c r="O38" t="n">
-        <v>142.7407798536111</v>
+        <v>19.16123595354574</v>
       </c>
       <c r="P38" t="n">
         <v>76.02154297439397</v>
@@ -37669,10 +37669,10 @@
         <v>152.0332477471097</v>
       </c>
       <c r="K39" t="n">
-        <v>236.9514395464517</v>
+        <v>235.973984628739</v>
       </c>
       <c r="L39" t="n">
-        <v>334.7616562800309</v>
+        <v>335.7391111977436</v>
       </c>
       <c r="M39" t="n">
         <v>158.8900421645043</v>
@@ -37827,7 +37827,7 @@
         <v>396</v>
       </c>
       <c r="K41" t="n">
-        <v>67.50108542713571</v>
+        <v>201.0761557454273</v>
       </c>
       <c r="L41" t="n">
         <v>83.74106532663313</v>
@@ -37839,13 +37839,13 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>396</v>
+        <v>19.16123595354574</v>
       </c>
       <c r="P41" t="n">
         <v>76.02154297439397</v>
       </c>
       <c r="Q41" t="n">
-        <v>152.7363062718372</v>
+        <v>396</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37912,13 +37912,13 @@
         <v>335.7391111977436</v>
       </c>
       <c r="M42" t="n">
-        <v>157.9125872467916</v>
+        <v>158.8900421645043</v>
       </c>
       <c r="N42" t="n">
         <v>208.4705878445039</v>
       </c>
       <c r="O42" t="n">
-        <v>309.0098898272747</v>
+        <v>308.0324349095619</v>
       </c>
       <c r="P42" t="n">
         <v>167.8831365901249</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
+        <v>9.995526418226255</v>
+      </c>
+      <c r="K44" t="n">
         <v>395</v>
-      </c>
-      <c r="K44" t="n">
-        <v>67.50108542713571</v>
       </c>
       <c r="L44" t="n">
         <v>83.74106532663313</v>
       </c>
       <c r="M44" t="n">
-        <v>132.6154743586956</v>
+        <v>395</v>
       </c>
       <c r="N44" t="n">
-        <v>395</v>
+        <v>190.1210333676051</v>
       </c>
       <c r="O44" t="n">
         <v>19.16123595354574</v>
@@ -38146,7 +38146,7 @@
         <v>236.9514395464517</v>
       </c>
       <c r="L45" t="n">
-        <v>330.802060320435</v>
+        <v>335.7391111977436</v>
       </c>
       <c r="M45" t="n">
         <v>158.8900421645043</v>
@@ -38155,7 +38155,7 @@
         <v>208.4705878445039</v>
       </c>
       <c r="O45" t="n">
-        <v>309.0098898272747</v>
+        <v>304.0728389499661</v>
       </c>
       <c r="P45" t="n">
         <v>167.8831365901249</v>
